--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView activeTab="0"/>
-  </bookViews>
   <sheets>
     <sheet state="visible" name="test_suite" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="validData" sheetId="2" r:id="rId5"/>
@@ -22,12 +19,13 @@
     <sheet state="visible" name="overAllAcademicsTest" sheetId="14" r:id="rId17"/>
     <sheet state="visible" name="CollegeUniversitiesTest" sheetId="15" r:id="rId18"/>
   </sheets>
+  <definedNames/>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="102">
   <si>
     <t>TCID</t>
   </si>
@@ -333,25 +331,12 @@
   </si>
   <si>
     <t>Test Degree</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>112419@test.asu.edu</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>May 24, 1988</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="0"/>
   <fonts count="10">
     <font>
       <sz val="11.0"/>
@@ -432,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -455,12 +440,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -728,11 +707,10 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1000"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="24.57"/>
-    <col min="2" max="6" customWidth="true" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="24.57"/>
+    <col customWidth="1" min="2" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2449,15 +2427,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="18.57"/>
-    <col min="7" max="7" customWidth="true" width="30.14"/>
+    <col customWidth="1" min="1" max="2" width="38.29"/>
+    <col customWidth="1" min="3" max="3" width="34.0"/>
+    <col customWidth="1" min="4" max="4" width="22.29"/>
+    <col customWidth="1" min="5" max="5" width="30.0"/>
+    <col customWidth="1" min="6" max="6" width="18.57"/>
+    <col customWidth="1" min="7" max="7" width="30.14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2552,14 +2529,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="2" width="38.29"/>
+    <col customWidth="1" min="3" max="3" width="34.0"/>
+    <col customWidth="1" min="4" max="4" width="22.29"/>
+    <col customWidth="1" min="5" max="5" width="30.0"/>
+    <col customWidth="1" min="6" max="6" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2636,14 +2612,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.14"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="41.43"/>
-    <col min="4" max="4" customWidth="true" width="34.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="27.14"/>
+    <col customWidth="1" min="2" max="2" width="29.57"/>
+    <col customWidth="1" min="3" max="3" width="41.43"/>
+    <col customWidth="1" min="4" max="4" width="34.43"/>
+    <col customWidth="1" min="5" max="5" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2711,10 +2686,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="5" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="5" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2901,10 +2875,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="4" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="4" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3001,14 +2974,13 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="31.0"/>
-    <col min="2" max="2" customWidth="true" width="27.43"/>
-    <col min="3" max="3" customWidth="true" width="51.0"/>
-    <col min="4" max="4" customWidth="true" width="22.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="31.0"/>
+    <col customWidth="1" min="2" max="2" width="27.43"/>
+    <col customWidth="1" min="3" max="3" width="51.0"/>
+    <col customWidth="1" min="4" max="4" width="22.43"/>
+    <col customWidth="1" min="5" max="5" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3075,26 +3047,20 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="36.86"/>
-    <col min="2" max="2" customWidth="true" width="41.14"/>
-    <col min="3" max="3" customWidth="true" width="20.43"/>
-    <col min="4" max="4" customWidth="true" width="20.14"/>
-    <col min="5" max="5" customWidth="true" width="31.43"/>
-    <col min="6" max="6" customWidth="true" width="24.43"/>
-    <col min="7" max="7" customWidth="true" width="26.71"/>
-    <col min="12" max="12" customWidth="true" width="40.71"/>
+    <col customWidth="1" min="1" max="1" width="36.86"/>
+    <col customWidth="1" min="2" max="2" width="41.14"/>
+    <col customWidth="1" min="3" max="3" width="20.43"/>
+    <col customWidth="1" min="4" max="4" width="20.14"/>
+    <col customWidth="1" min="5" max="5" width="31.43"/>
+    <col customWidth="1" min="6" max="6" width="24.43"/>
+    <col customWidth="1" min="7" max="7" width="26.71"/>
+    <col customWidth="1" min="12" max="12" width="40.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" t="s" s="0">
-        <v>102</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>103</v>
-      </c>
+      <c r="B1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="4"/>
       <c r="F1" s="3"/>
@@ -3124,12 +3090,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>104</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>105</v>
-      </c>
+      <c r="A4" s="4"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="4"/>
       <c r="F4" s="3"/>
@@ -5236,15 +5198,14 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="13.14"/>
-    <col min="2" max="2" customWidth="true" width="23.71"/>
-    <col min="3" max="3" customWidth="true" width="45.14"/>
-    <col min="4" max="4" customWidth="true" width="14.57"/>
-    <col min="5" max="5" customWidth="true" width="60.0"/>
-    <col min="6" max="6" customWidth="true" width="25.14"/>
+    <col customWidth="1" min="1" max="1" width="13.14"/>
+    <col customWidth="1" min="2" max="2" width="23.71"/>
+    <col customWidth="1" min="3" max="3" width="45.14"/>
+    <col customWidth="1" min="4" max="4" width="14.57"/>
+    <col customWidth="1" min="5" max="5" width="60.0"/>
+    <col customWidth="1" min="6" max="6" width="25.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7307,15 +7268,14 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.29"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="24.57"/>
-    <col min="4" max="4" customWidth="true" width="27.57"/>
-    <col min="5" max="5" customWidth="true" width="25.29"/>
-    <col min="6" max="6" customWidth="true" width="33.57"/>
+    <col customWidth="1" min="1" max="1" width="37.29"/>
+    <col customWidth="1" min="2" max="2" width="29.57"/>
+    <col customWidth="1" min="3" max="3" width="24.57"/>
+    <col customWidth="1" min="4" max="4" width="27.57"/>
+    <col customWidth="1" min="5" max="5" width="25.29"/>
+    <col customWidth="1" min="6" max="6" width="33.57"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9374,12 +9334,11 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="14.14"/>
-    <col min="3" max="3" customWidth="true" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="27.29"/>
+    <col customWidth="1" min="2" max="2" width="14.14"/>
+    <col customWidth="1" min="3" max="3" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9442,14 +9401,13 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="29.43"/>
-    <col min="2" max="2" customWidth="true" width="31.43"/>
-    <col min="3" max="3" customWidth="true" width="28.71"/>
-    <col min="4" max="4" customWidth="true" width="30.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="29.43"/>
+    <col customWidth="1" min="2" max="2" width="31.43"/>
+    <col customWidth="1" min="3" max="3" width="28.71"/>
+    <col customWidth="1" min="4" max="4" width="30.57"/>
+    <col customWidth="1" min="5" max="5" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9567,13 +9525,12 @@
   <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="20.14"/>
-    <col min="3" max="4" customWidth="true" width="13.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="27.29"/>
+    <col customWidth="1" min="2" max="2" width="20.14"/>
+    <col customWidth="1" min="3" max="4" width="13.57"/>
+    <col customWidth="1" min="5" max="5" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9675,12 +9632,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.57"/>
-    <col min="2" max="2" customWidth="true" width="39.86"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="27.57"/>
+    <col customWidth="1" min="2" max="2" width="39.86"/>
+    <col customWidth="1" min="3" max="3" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9862,12 +9818,11 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="56.0"/>
-    <col min="2" max="2" customWidth="true" width="57.0"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col customWidth="1" min="1" max="1" width="56.0"/>
+    <col customWidth="1" min="2" max="2" width="57.0"/>
+    <col customWidth="1" min="3" max="3" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -3,11 +3,11 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\divya\git\undergrad\UAA\src\src\test\resources\com\ugapp\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\divya\git\undergrad\UAA\src\src\test\resources\com\ugapp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="test_suite" sheetId="1" r:id="rId1"/>
@@ -25,13 +25,14 @@
     <sheet name="AddMaxHighSchoolTest" sheetId="13" r:id="rId13"/>
     <sheet name="overAllAcademicsTest" sheetId="14" r:id="rId14"/>
     <sheet name="CollegeUniversitiesTest" sheetId="15" r:id="rId15"/>
+    <sheet name="Mismatch_01_valid_vs_Revie" r:id="rId19" sheetId="16"/>
   </sheets>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="63">
   <si>
     <t>TCID</t>
   </si>
@@ -69,654 +70,723 @@
     <t>overAllAcademicsTest</t>
   </si>
   <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>Testug</t>
+  </si>
+  <si>
+    <t>Testug@1test.asu.edu</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>testug@test.asu.edu</t>
+  </si>
+  <si>
+    <t>Test123123123</t>
+  </si>
+  <si>
+    <t>firstname</t>
+  </si>
+  <si>
+    <t>preferredfirstname</t>
+  </si>
+  <si>
+    <t>middlename</t>
+  </si>
+  <si>
+    <t>lastname</t>
+  </si>
+  <si>
+    <t>Test1</t>
+  </si>
+  <si>
+    <t>Test@</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Test </t>
+  </si>
+  <si>
+    <t>TestTestTestTestTestTestTest</t>
+  </si>
+  <si>
+    <t>TestTestTestTestTestTestTestTest</t>
+  </si>
+  <si>
+    <t>Test FN</t>
+  </si>
+  <si>
+    <t>Automation PFN</t>
+  </si>
+  <si>
+    <t>Automation MN</t>
+  </si>
+  <si>
+    <t>Test LN</t>
+  </si>
+  <si>
+    <t>reemail</t>
+  </si>
+  <si>
+    <t>repassword</t>
+  </si>
+  <si>
+    <t>embtest@test.asu.edu</t>
+  </si>
+  <si>
+    <t>test123123123</t>
+  </si>
+  <si>
+    <t>Testsadasda</t>
+  </si>
+  <si>
+    <t>First_name</t>
+  </si>
+  <si>
+    <t>Last_name</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Test First Name</t>
+  </si>
+  <si>
+    <t>Test Last Name</t>
+  </si>
+  <si>
+    <t>TestTestTestTestTestTestTestTestTestTestTestTestTestTestTest</t>
+  </si>
+  <si>
+    <t>Parent FN</t>
+  </si>
+  <si>
+    <t>Parent LN I</t>
+  </si>
+  <si>
+    <t>Parent LN II</t>
+  </si>
+  <si>
+    <t>AddressLine1</t>
+  </si>
+  <si>
+    <t>AddressLine2</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Zip</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Phone_Number</t>
+  </si>
+  <si>
+    <t>Mobile_Number</t>
+  </si>
+  <si>
+    <t>TestTestTestTestTestTestTestTestTestTestTestTestTest</t>
+  </si>
+  <si>
+    <t>1111111111111111</t>
+  </si>
+  <si>
+    <t>@</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>Test Address line1</t>
+  </si>
+  <si>
+    <t>Test Address line2</t>
+  </si>
+  <si>
+    <t>Test City</t>
+  </si>
+  <si>
+    <t>12345-678910</t>
+  </si>
+  <si>
+    <t>Test State</t>
+  </si>
+  <si>
+    <t>6363052399</t>
+  </si>
+  <si>
+    <t>8150052399</t>
+  </si>
+  <si>
+    <t>TestTestTestTestTestTestTestTestTestTestTest</t>
+  </si>
+  <si>
+    <t>SAISno</t>
+  </si>
+  <si>
+    <t>School_name</t>
+  </si>
+  <si>
+    <t>testtesttesttesttesttesttesttest</t>
+  </si>
+  <si>
+    <t>12345678910</t>
+  </si>
+  <si>
+    <t>1234567890</t>
+  </si>
+  <si>
+    <t>Test School</t>
+  </si>
+  <si>
+    <t>1234567891</t>
+  </si>
+  <si>
+    <t>Test School A</t>
+  </si>
+  <si>
+    <t>Test School B</t>
+  </si>
+  <si>
+    <t>Test School C</t>
+  </si>
+  <si>
+    <t>Test School D</t>
+  </si>
+  <si>
+    <t>Test School E</t>
+  </si>
+  <si>
+    <t>Test School F</t>
+  </si>
+  <si>
+    <t>Test School G</t>
+  </si>
+  <si>
+    <t>Test School H</t>
+  </si>
+  <si>
+    <t>Test School I</t>
+  </si>
+  <si>
+    <t>unweightedGPA</t>
+  </si>
+  <si>
+    <t>classrank</t>
+  </si>
+  <si>
+    <t>classSize</t>
+  </si>
+  <si>
+    <t>1234567</t>
+  </si>
+  <si>
+    <t>12345</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Institution_name</t>
+  </si>
+  <si>
+    <t>Degree_Concentration</t>
+  </si>
+  <si>
+    <t>testtesttesttesttesttesttesttesttesttesttesttesttesttesttest</t>
+  </si>
+  <si>
+    <t>Test Institution</t>
+  </si>
+  <si>
+    <t>Test Degree</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>5382521@test.asu.edu</t>
+  </si>
+  <si>
+    <t>Legal name</t>
+  </si>
+  <si>
+    <t>Test FN Automation MN Test LN</t>
+  </si>
+  <si>
+    <t>Preferred first name</t>
+  </si>
+  <si>
     <t>Legal sex</t>
   </si>
   <si>
-    <t>X or another legal sex</t>
+    <t>Female</t>
   </si>
   <si>
     <t>Primary language spoken at home</t>
   </si>
   <si>
-    <t>Bavarian</t>
+    <t>Chhattisgarhi</t>
   </si>
   <si>
     <t>Home address</t>
   </si>
   <si>
-    <t>Test Address line1 Test Address line2
-TestTestTestTestTestTestTestTest,Test State,Mayotte
+    <t>Test Address Line I Test Address Line II
+Test City,Arizona,United States
+United States
+Afghanistan
+Aland Islands
+Albania
+Algeria
+American Samoa
+Andorra
+Angola
+Anguilla
+Antarctica
+Antigua and Barbuda
+Argentina
+Armenia
+Aruba
+Australia
+Austria
+Azerbaijan
+Bahamas, The
+Bahrain
+Bangladesh
+Barbados
+Belarus
+Belgium
+Belize
+Benin
+Bermuda
+Bhutan
+Bolivia
+Bonaire, Sint Eustatius &amp; Saba
+Bosnia and Herzegovina
+Botswana
+Bouvet Island
+Brazil
+British Indian Ocean Territory
+British Virgin Islands
+Brunei
+Bulgaria
+Burkina Faso
+Burma
+Burundi
+Cambodia
+Cameroon
+Canada
+Cape Verde
+Cayman Islands
+Central African Republic
+Chad
+Chile
+China
+Christmas Island
+Cocos (Keeling) Islands
+Colombia
+Comoros
+Congo
+Congo, Democratic Republic of
+Cook Islands
+Costa Rica
+Cote D'Ivoire
+Croatia
+Cuba
+Curacao
+Cyprus
+Czech Republic
+Denmark
+Djibouti
+Dominica
+Dominican Republic
+Ecuador
+Egypt
+El Salvador
+Equatorial Guinea
+Eritrea
+Estonia
+Eswatini
+Ethiopia
+Falkland Islands (Malvinas)
+Faroe Islands
+Fiji
+Finland
+France
+French Guiana
+French Polynesia
+French Southern &amp; Antarc Lands
+Gabon
+Gambia, The
+Georgia
+Germany
+Ghana
+Gibraltar
+Greece
+Greenland
+Grenada
+Guadeloupe
+Guam
+Guatemala
+Guernsey
+Guinea
+Guinea-Bissau
+Guyana
+Haiti
+Heard and McDonald Islands
+Honduras
+Hong Kong
+Hungary
+Iceland
+India
+Indonesia
+Iran
+Iraq
+Ireland
+Isle of Man
+Israel
+Italy
+Jamaica
+Japan
+Jersey
+Jordan
+Kazakhstan
+Kenya
+Kiribati
+Kosovo
+Kuwait
+Kyrgyzstan
+Laos
+Latvia
+Lebanon
+Lesotho
+Liberia
+Libya
+Liechtenstein
+Lithuania
+Luxembourg
+Macau
+Madagascar
+Malawi
+Malaysia
+Maldives
+Mali
+Malta
+Marshall Islands
+Martinique
+Mauritania
+Mauritius
+Mayotte
+Mexico
+Micronesia, Federated States
+Moldova
+Monaco
+Mongolia
+Montenegro
+Montserrat
+Morocco
+Mozambique
+Namibia
+Nauru
+Nepal
+Netherlands
+Netherlands Antilles
+New Caledonia
+New Zealand
+Nicaragua
+Niger
+Nigeria
+Niue
+Norfolk Island
+North Korea
+Northern Mariana Islands
+Norway
+Oman
+Pakistan
+Palau
+Palestinian Territory, Occupie
+Panama
+Papua New Guinea
+Paraguay
+Peru
+Philippines
+Pitcairn Islands
+Poland
+Portugal
+Puerto Rico
+Qatar
+Republic of North Macedonia
+Reunion
+Romania
+Russia
+Rwanda
+Saint Barthelemy
+Saint Helena
+Saint Kitts and Nevis
+Saint Lucia
+Saint Martin
+Saint Pierre and Miquelon
+Saint Vincent &amp; the Grenadines
+Samoa
+San Marino
+Sao Tome and Principe
+Saudi Arabia
+Senegal
+Serbia
+Seychelles
+Sierra Leone
+Singapore
+Sint Maarten (Dutch part)
+Slovakia
+Slovenia
+Solomon Islands
+Somalia
+South Africa
+South Georgia &amp; S Sandwich Is
+South Korea
+South Sudan
+Spain
+Spratly Islands
+Sri Lanka
+Sudan
+Suriname
+Svalbard and Jan Mayen
+Sweden
+Switzerland
+Syria
+Taiwan
+Tajikistan
+Tanzania
+Thailand
+Timor-Leste
+Togo
+Tokelau
+Tonga
+Trinidad and Tobago
+Tunisia
+Turkey
+Turkmenistan
+Turks and Caicos Islands
+Tuvalu
+US Misc Pacific Islands
+Uganda
+Ukraine
+United Arab Emirates
+United Kingdom
+Uruguay
+Uzbekistan
+Vanuatu
+Vatican City
+Venezuela
+Vietnam
+Virgin Islands
+Wallis and Futuna Islands
+Western Sahara
+Yemen
+Yugoslavia
+Zambia
+Zimbabwe
 12345-678910</t>
   </si>
   <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>Testug</t>
-  </si>
-  <si>
-    <t>Testug@1test.asu.edu</t>
-  </si>
-  <si>
-    <t>test</t>
-  </si>
-  <si>
-    <t>testug@test.asu.edu</t>
-  </si>
-  <si>
-    <t>Test123123123</t>
-  </si>
-  <si>
-    <t>firstname</t>
-  </si>
-  <si>
-    <t>preferredfirstname</t>
-  </si>
-  <si>
-    <t>middlename</t>
-  </si>
-  <si>
-    <t>lastname</t>
-  </si>
-  <si>
-    <t>Test1</t>
-  </si>
-  <si>
-    <t>Test@</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Test </t>
-  </si>
-  <si>
-    <t>TestTestTestTestTestTestTest</t>
-  </si>
-  <si>
-    <t>TestTestTestTestTestTestTestTest</t>
-  </si>
-  <si>
-    <t>Test FN</t>
-  </si>
-  <si>
-    <t>Automation PFN</t>
-  </si>
-  <si>
-    <t>Automation MN</t>
-  </si>
-  <si>
-    <t>Test LN</t>
-  </si>
-  <si>
-    <t>reemail</t>
-  </si>
-  <si>
-    <t>repassword</t>
-  </si>
-  <si>
-    <t>embtest@test.asu.edu</t>
-  </si>
-  <si>
-    <t>test123123123</t>
-  </si>
-  <si>
-    <t>Testsadasda</t>
-  </si>
-  <si>
-    <t>First_name</t>
-  </si>
-  <si>
-    <t>Last_name</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Test First Name</t>
-  </si>
-  <si>
-    <t>Test Last Name</t>
-  </si>
-  <si>
-    <t>TestTestTestTestTestTestTestTestTestTestTestTestTestTestTest</t>
-  </si>
-  <si>
-    <t>Parent FN</t>
-  </si>
-  <si>
-    <t>Parent LN I</t>
-  </si>
-  <si>
-    <t>Parent LN II</t>
-  </si>
-  <si>
-    <t>AddressLine1</t>
-  </si>
-  <si>
-    <t>AddressLine2</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Zip</t>
-  </si>
-  <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Phone_Number</t>
-  </si>
-  <si>
-    <t>Mobile_Number</t>
-  </si>
-  <si>
-    <t>TestTestTestTestTestTestTestTestTestTestTestTestTest</t>
-  </si>
-  <si>
-    <t>1111111111111111</t>
-  </si>
-  <si>
-    <t>@</t>
-  </si>
-  <si>
-    <t>abc</t>
-  </si>
-  <si>
-    <t>Test Address line1</t>
-  </si>
-  <si>
-    <t>Test Address line2</t>
-  </si>
-  <si>
-    <t>Test City</t>
-  </si>
-  <si>
-    <t>12345-678910</t>
-  </si>
-  <si>
-    <t>Test State</t>
-  </si>
-  <si>
-    <t>6363052399</t>
-  </si>
-  <si>
-    <t>8150052399</t>
-  </si>
-  <si>
-    <t>TestTestTestTestTestTestTestTestTestTestTest</t>
-  </si>
-  <si>
-    <t>SAISno</t>
-  </si>
-  <si>
-    <t>School_name</t>
-  </si>
-  <si>
-    <t>testtesttesttesttesttesttesttest</t>
-  </si>
-  <si>
-    <t>12345678910</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
-    <t>Test School</t>
-  </si>
-  <si>
-    <t>1234567891</t>
-  </si>
-  <si>
-    <t>Test School A</t>
-  </si>
-  <si>
-    <t>Test School B</t>
-  </si>
-  <si>
-    <t>Test School C</t>
-  </si>
-  <si>
-    <t>Test School D</t>
-  </si>
-  <si>
-    <t>Test School E</t>
-  </si>
-  <si>
-    <t>Test School F</t>
-  </si>
-  <si>
-    <t>Test School G</t>
-  </si>
-  <si>
-    <t>Test School H</t>
-  </si>
-  <si>
-    <t>Test School I</t>
-  </si>
-  <si>
-    <t>unweightedGPA</t>
-  </si>
-  <si>
-    <t>classrank</t>
-  </si>
-  <si>
-    <t>classSize</t>
-  </si>
-  <si>
-    <t>1234567</t>
-  </si>
-  <si>
-    <t>12345</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Institution_name</t>
-  </si>
-  <si>
-    <t>Degree_Concentration</t>
-  </si>
-  <si>
-    <t>testtesttesttesttesttesttesttesttesttesttesttesttesttesttest</t>
-  </si>
-  <si>
-    <t>Test Institution</t>
-  </si>
-  <si>
-    <t>Test Degree</t>
-  </si>
-  <si>
-    <t>Legal name</t>
-  </si>
-  <si>
-    <t>Test FN Automation MN Test LN</t>
-  </si>
-  <si>
-    <t>Preferred first name</t>
+    <t>U.S. citizenship</t>
+  </si>
+  <si>
+    <t>I am a U.S. citizen</t>
+  </si>
+  <si>
+    <t>Country of citizenship</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>Country of birth</t>
+  </si>
+  <si>
+    <t>South Korea</t>
+  </si>
+  <si>
+    <t>Social Security Number</t>
+  </si>
+  <si>
+    <t>*********</t>
+  </si>
+  <si>
+    <t>Previous ASU affiliation</t>
+  </si>
+  <si>
+    <t>I have never been affiliated with Arizona State University</t>
+  </si>
+  <si>
+    <t>Military status</t>
+  </si>
+  <si>
+    <t>None of these options apply to me</t>
+  </si>
+  <si>
+    <t>Do you plan to use an education benefit or scholarship through an employer, corporation, foundation or other ASU education partner?</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Graduating school </t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>High school name</t>
+  </si>
+  <si>
+    <t>Name on transcript</t>
+  </si>
+  <si>
+    <t>Test FN Test LN</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Test City, BS, GNQ</t>
+  </si>
+  <si>
+    <t>Graduation date</t>
+  </si>
+  <si>
+    <t>July, 2027</t>
+  </si>
+  <si>
+    <t>Transfer credits to ASU</t>
+  </si>
+  <si>
+    <t>Begin by selecting the state you consider to be your permanent home.</t>
+  </si>
+  <si>
+    <t>Outside the U.S. or Not Listed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In which state do your parent(s) or legal guardian(s) currently live? </t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
   </si>
   <si>
     <t>Date of birth</t>
   </si>
   <si>
-    <t>September 23, 1968</t>
-  </si>
-  <si>
-    <t>Magahi</t>
-  </si>
-  <si>
-    <t>Test Address line1 Test Address line2
-TestTestTestTestTestTestTestTest,Test State,Falkland Islands (Malvinas)
+    <t>November 11, 2010</t>
+  </si>
+  <si>
+    <t>Pronouns</t>
+  </si>
+  <si>
+    <t>No data has been entered</t>
+  </si>
+  <si>
+    <t>Gender identity</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>+1 (234) 567-6543</t>
+  </si>
+  <si>
+    <t>Mobile phone</t>
+  </si>
+  <si>
+    <t>Mobile SMS</t>
+  </si>
+  <si>
+    <t>Former name(s)</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Test Address Line I Test Address Line II
+Test City,Arizona,United States
 12345-678910</t>
   </si>
   <si>
-    <t>Test Address line1 Test Address line2
-Test City,Test State,Falkland Islands (Malvinas)
-12345-678910</t>
-  </si>
-  <si>
-    <t>U.S. citizenship</t>
-  </si>
-  <si>
-    <t>I am a U.S. citizen</t>
-  </si>
-  <si>
-    <t>Country of citizenship</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Country of birth</t>
-  </si>
-  <si>
-    <t>United Arab Emirates</t>
-  </si>
-  <si>
-    <t>Social Security Number</t>
-  </si>
-  <si>
-    <t>*********</t>
-  </si>
-  <si>
-    <t>Parent or Legal Guardian Attended ASU</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Parent or legal guardian</t>
-  </si>
-  <si>
-    <t>Parent FN Parent LN I</t>
-  </si>
-  <si>
-    <t>Parent or Legal Guardian Relation</t>
-  </si>
-  <si>
-    <t>Father</t>
-  </si>
-  <si>
-    <t>Parent or Legal Guardian Schooling Level</t>
-  </si>
-  <si>
-    <t>Middle School/Junior High</t>
-  </si>
-  <si>
-    <t>Additional parent or legal guardian</t>
-  </si>
-  <si>
-    <t>Parent FN Parent LN II</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Other/Unknown</t>
-  </si>
-  <si>
-    <t>Previous ASU affiliation</t>
-  </si>
-  <si>
-    <t>I have never been affiliated with Arizona State University</t>
-  </si>
-  <si>
-    <t>Military status</t>
-  </si>
-  <si>
-    <t>I am the spouse/dependent of a U.S. service member or veteran</t>
-  </si>
-  <si>
-    <t>Branch</t>
-  </si>
-  <si>
-    <t>United States Space Force
-United States Army
-United States Marine Corps
-United States Navy
-United States Air Force
-United States Coast Guard
-United States Space Force
-United States Public Health Service Commissioned Corps
-National Oceanic and Atmospheric Administration Commissioned Officer Corps</t>
-  </si>
-  <si>
-    <t>I have applied or plan to apply for Department of Veterans Affairs educational benefits based on my U.S. services affiliation identified above:</t>
-  </si>
-  <si>
-    <t>Do you plan to use an education benefit or scholarship through an employer, corporation, foundation or other ASU education partner?</t>
-  </si>
-  <si>
-    <t>Pre-law interest</t>
-  </si>
-  <si>
-    <t>Pre-med/health interest</t>
-  </si>
-  <si>
-    <t>Pre-veterinary interest</t>
-  </si>
-  <si>
-    <t>Teaching certificate interest</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>9510580@test.asu.edu</t>
-  </si>
-  <si>
-    <t>March 21, 1973</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Nepali</t>
-  </si>
-  <si>
-    <t>Test Address line1 Test Address line2
-TestTestTestTestTestTestTestTest,Diber,Albania
-12345-678910</t>
-  </si>
-  <si>
-    <t>Test Address line1 Test Address line2
-Test City,Elbasan,Albania
-12345-678910</t>
-  </si>
-  <si>
-    <t>Saint Helena</t>
-  </si>
-  <si>
-    <t>Aunt</t>
-  </si>
-  <si>
-    <t>College or Beyond</t>
-  </si>
-  <si>
-    <t>National Oceanic and Atmospheric Administration Commissioned Officer Corps
-United States Army
-United States Marine Corps
-United States Navy
-United States Air Force
-United States Coast Guard
-United States Space Force
-United States Public Health Service Commissioned Corps
-National Oceanic and Atmospheric Administration Commissioned Officer Corps</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Graduating school </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>High school name</t>
-  </si>
-  <si>
-    <t>Name on transcript</t>
-  </si>
-  <si>
-    <t>Test FN Test LN</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Test City, CO, MCO</t>
-  </si>
-  <si>
-    <t>Transfer credits to ASU</t>
-  </si>
-  <si>
-    <t>Test City, ALT, RUS</t>
-  </si>
-  <si>
-    <t>Graduation date</t>
-  </si>
-  <si>
-    <t>January, 2028</t>
-  </si>
-  <si>
-    <t>Test City, SIL, TUN</t>
-  </si>
-  <si>
-    <t>May, 2026</t>
-  </si>
-  <si>
-    <t>Begin by selecting the state you consider to be your permanent home.</t>
-  </si>
-  <si>
-    <t>Outside the U.S. or Not Listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In which state do your parent(s) or legal guardian(s) currently live? </t>
-  </si>
-  <si>
-    <t>Arizona</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Which parent or legal guardian lives in Arizona? </t>
-  </si>
-  <si>
-    <t>Both</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Did or will your parent(s) or legal guardian(s) file a state income tax return for the 2022 tax year? </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Does either parent or legal guardian have a current Arizona driver license? </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Is either parent or legal guardian employed in Arizona? </t>
-  </si>
-  <si>
-    <t>6115547@test.asu.eduqq</t>
-  </si>
-  <si>
-    <t>8633249@test.asu.eduqq</t>
-  </si>
-  <si>
-    <t>9462637@`yagfsgdhs.jsdk.js</t>
-  </si>
-  <si>
-    <t>9603168@yagfsgdhs.jsdk.js</t>
-  </si>
-  <si>
-    <t>4703089@yahoo.com</t>
-  </si>
-  <si>
-    <t>6081021@yahoo.com</t>
-  </si>
-  <si>
-    <t>6483262@yahoo.com</t>
-  </si>
-  <si>
-    <t>5794280@yahoo.com</t>
-  </si>
-  <si>
-    <t>4388084@yahoo.com</t>
-  </si>
-  <si>
-    <t>6343577@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7744485@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>5699133@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7494977@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>1981065@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>9860599@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>9886703@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>5653567@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>4201940@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7858486@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>9484638@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7899495@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7217096@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>8722881@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>2912360@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>2189433@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>8793460@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7761037@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>2254454@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>3809820@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>5251453@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>3968001@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>6831980@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>5410896@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>4348566@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>4525040@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>7227262@yahoo.com.sh</t>
-  </si>
-  <si>
-    <t>1209305@yahoo.com.sh</t>
+    <t>Ethnic/racial background</t>
+  </si>
+  <si>
+    <t>Affiliate ID</t>
+  </si>
+  <si>
+    <t>Program</t>
+  </si>
+  <si>
+    <t>Nondegree</t>
+  </si>
+  <si>
+    <t>ASU Online</t>
+  </si>
+  <si>
+    <t>Starting term</t>
+  </si>
+  <si>
+    <t>Fall 2025 - (Session B)</t>
+  </si>
+  <si>
+    <t>Graduating school</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Value Sheet 1</t>
+  </si>
+  <si>
+    <t>Value Sheet 2</t>
+  </si>
+  <si>
+    <t>In which state do your parent(s) or legal guardian(s) currently live?</t>
   </si>
 </sst>
 </file>
@@ -795,7 +865,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -818,96 +888,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
@@ -3102,25 +3082,25 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -3128,25 +3108,25 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>3</v>
@@ -3154,25 +3134,25 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>78</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>3</v>
@@ -3201,19 +3181,19 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
@@ -3221,19 +3201,19 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>3</v>
@@ -3241,19 +3221,19 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>3</v>
@@ -3282,16 +3262,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -3299,16 +3279,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -3316,16 +3296,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -3350,16 +3330,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -3367,16 +3347,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -3384,16 +3364,16 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -3401,16 +3381,16 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -3418,16 +3398,16 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -3435,16 +3415,16 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
@@ -3452,16 +3432,16 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C7" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>3</v>
@@ -3469,16 +3449,16 @@
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>3</v>
@@ -3486,16 +3466,16 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>3</v>
@@ -3503,16 +3483,16 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>3</v>
@@ -3537,13 +3517,13 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
@@ -3551,13 +3531,13 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
@@ -3565,13 +3545,13 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>3</v>
@@ -3579,13 +3559,13 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -3594,10 +3574,10 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="11"/>
       <c r="B5" s="12" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -3606,10 +3586,10 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="11"/>
       <c r="B6" s="12" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>3</v>
@@ -3638,16 +3618,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -3655,16 +3635,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -3672,16 +3652,16 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -3690,6 +3670,38 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
 
@@ -3710,10 +3722,10 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="B1" s="128" t="s">
-        <v>219</v>
+        <v>103</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
@@ -3725,10 +3737,10 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s" s="0">
-        <v>109</v>
-      </c>
-      <c r="B2" s="43" t="s">
-        <v>110</v>
+        <v>105</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>106</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
@@ -3739,10 +3751,10 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s" s="0">
-        <v>111</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>35</v>
+        <v>107</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>29</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
@@ -3752,12 +3764,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>152</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -3796,10 +3804,10 @@
     </row>
     <row r="8" ht="14.25" customHeight="1">
       <c r="A8" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B8" s="46" t="s">
-        <v>153</v>
+        <v>108</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
@@ -3810,10 +3818,10 @@
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="B9" s="47" t="s">
-        <v>154</v>
+        <v>110</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>111</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
@@ -3824,10 +3832,10 @@
     </row>
     <row r="10" ht="137.25" customHeight="1">
       <c r="A10" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="B10" s="49" t="s">
-        <v>156</v>
+        <v>112</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>113</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
@@ -3871,10 +3879,10 @@
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" t="s" s="0">
-        <v>117</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>118</v>
+        <v>114</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>115</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
@@ -3885,10 +3893,10 @@
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" t="s" s="0">
-        <v>119</v>
-      </c>
-      <c r="B15" s="51" t="s">
-        <v>120</v>
+        <v>116</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>117</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
@@ -3899,10 +3907,10 @@
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" t="s" s="0">
-        <v>121</v>
-      </c>
-      <c r="B16" s="52" t="s">
-        <v>157</v>
+        <v>118</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>119</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
@@ -3913,10 +3921,10 @@
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" t="s" s="0">
-        <v>123</v>
-      </c>
-      <c r="B17" s="53" t="s">
-        <v>124</v>
+        <v>120</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>121</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
@@ -3934,68 +3942,39 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="B19" s="54" t="s">
-        <v>129</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="3"/>
       <c r="H19" s="3"/>
       <c r="K19" s="1"/>
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B20" s="55" t="s">
-        <v>158</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="3"/>
       <c r="H20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" t="s" s="0">
-        <v>132</v>
-      </c>
-      <c r="B21" s="56" t="s">
-        <v>159</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="3"/>
       <c r="H21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" t="s" s="0">
-        <v>125</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>127</v>
-      </c>
+      <c r="B22" s="3"/>
       <c r="H22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" t="s" s="0">
-        <v>134</v>
-      </c>
-      <c r="B23" s="57" t="s">
-        <v>135</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="3"/>
       <c r="H23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B24" s="58" t="s">
-        <v>136</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="3"/>
       <c r="H24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" t="s" s="0">
-        <v>132</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>159</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="3"/>
       <c r="H25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
@@ -4003,10 +3982,10 @@
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="B27" s="60" t="s">
-        <v>139</v>
+        <v>122</v>
+      </c>
+      <c r="B27" s="24" t="s">
+        <v>123</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="1"/>
@@ -4027,10 +4006,10 @@
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" t="s" s="0">
-        <v>140</v>
-      </c>
-      <c r="B29" s="61" t="s">
-        <v>141</v>
+        <v>124</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="1"/>
@@ -4041,12 +4020,8 @@
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="B30" s="62" t="s">
-        <v>160</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="1"/>
       <c r="F30" s="3"/>
@@ -4054,12 +4029,8 @@
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="B31" s="63" t="s">
-        <v>127</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
       <c r="F31" s="3"/>
@@ -4076,9 +4047,9 @@
     </row>
     <row r="33" ht="14.25" customHeight="1">
       <c r="A33" t="s" s="0">
-        <v>145</v>
-      </c>
-      <c r="B33" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B33" s="26" t="s">
         <v>127</v>
       </c>
       <c r="D33" s="3"/>
@@ -4160,12 +4131,8 @@
       <c r="J40" s="3"/>
     </row>
     <row r="41" ht="14.25" customHeight="1">
-      <c r="A41" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B41" s="65" t="s">
-        <v>127</v>
-      </c>
+      <c r="A41" s="1"/>
+      <c r="B41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="1"/>
       <c r="F41" s="3"/>
@@ -4176,12 +4143,8 @@
       <c r="L41" s="3"/>
     </row>
     <row r="42" ht="14.25" customHeight="1">
-      <c r="A42" t="s" s="0">
-        <v>147</v>
-      </c>
-      <c r="B42" s="66" t="s">
-        <v>126</v>
-      </c>
+      <c r="A42" s="1"/>
+      <c r="B42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="1"/>
       <c r="F42" s="3"/>
@@ -4192,12 +4155,8 @@
       <c r="L42" s="3"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
-      <c r="A43" t="s" s="0">
-        <v>148</v>
-      </c>
-      <c r="B43" s="67" t="s">
-        <v>127</v>
-      </c>
+      <c r="A43" s="1"/>
+      <c r="B43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="1"/>
       <c r="F43" s="3"/>
@@ -4208,12 +4167,8 @@
       <c r="L43" s="3"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
-      <c r="A44" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B44" s="68" t="s">
-        <v>126</v>
-      </c>
+      <c r="A44" s="1"/>
+      <c r="B44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="1"/>
       <c r="F44" s="3"/>
@@ -4225,10 +4180,10 @@
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" t="s" s="0">
-        <v>161</v>
-      </c>
-      <c r="B45" s="80" t="s">
-        <v>162</v>
+        <v>128</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>129</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="1"/>
@@ -4241,10 +4196,10 @@
     </row>
     <row r="46" ht="14.25" customHeight="1">
       <c r="A46" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="B46" s="81" t="s">
-        <v>85</v>
+        <v>130</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>79</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="1"/>
@@ -4257,10 +4212,10 @@
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="B47" s="82" t="s">
-        <v>165</v>
+        <v>131</v>
+      </c>
+      <c r="B47" s="29" t="s">
+        <v>132</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="1"/>
@@ -4273,10 +4228,10 @@
     </row>
     <row r="48" ht="14.25" customHeight="1">
       <c r="A48" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="B48" s="83" t="s">
-        <v>172</v>
+        <v>133</v>
+      </c>
+      <c r="B48" s="30" t="s">
+        <v>134</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="1"/>
@@ -4289,10 +4244,10 @@
     </row>
     <row r="49" ht="14.25" customHeight="1">
       <c r="A49" t="s" s="0">
-        <v>170</v>
-      </c>
-      <c r="B49" s="84" t="s">
-        <v>173</v>
+        <v>135</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>136</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="1"/>
@@ -4305,10 +4260,10 @@
     </row>
     <row r="50" ht="14.25" customHeight="1">
       <c r="A50" t="s" s="0">
-        <v>168</v>
-      </c>
-      <c r="B50" s="85" t="s">
-        <v>103</v>
+        <v>137</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>97</v>
       </c>
       <c r="D50" s="3"/>
       <c r="H50" s="3"/>
@@ -4801,10 +4756,10 @@
     </row>
     <row r="126" ht="14.25" customHeight="1">
       <c r="A126" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="B126" s="86" t="s">
-        <v>175</v>
+        <v>138</v>
+      </c>
+      <c r="B126" s="33" t="s">
+        <v>139</v>
       </c>
       <c r="D126" s="3"/>
       <c r="E126" s="1"/>
@@ -5068,44 +5023,22 @@
     </row>
     <row r="178" ht="14.25" customHeight="1">
       <c r="A178" t="s" s="0">
-        <v>176</v>
-      </c>
-      <c r="B178" s="87" t="s">
-        <v>177</v>
+        <v>140</v>
+      </c>
+      <c r="B178" s="34" t="s">
+        <v>141</v>
       </c>
       <c r="D178" s="3"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
-      <c r="A179" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="B179" s="88" t="s">
-        <v>179</v>
-      </c>
+      <c r="B179" s="3"/>
     </row>
     <row r="180" ht="14.25" customHeight="1">
-      <c r="A180" t="s" s="0">
-        <v>180</v>
-      </c>
-      <c r="B180" s="89" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="181" ht="14.25" customHeight="1">
-      <c r="A181" t="s" s="0">
-        <v>181</v>
-      </c>
-      <c r="B181" s="90" t="s">
-        <v>127</v>
-      </c>
-    </row>
+      <c r="B180" s="3"/>
+    </row>
+    <row r="181" ht="14.25" customHeight="1"/>
     <row r="182" ht="14.25" customHeight="1">
-      <c r="A182" t="s" s="0">
-        <v>182</v>
-      </c>
-      <c r="B182" s="91" t="s">
-        <v>126</v>
-      </c>
+      <c r="B182" s="3"/>
     </row>
     <row r="183" ht="14.25" customHeight="1">
       <c r="B183" s="3"/>
@@ -6019,8 +5952,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="3"/>
+      <c r="A1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B1" s="35" t="s">
+        <v>106</v>
+      </c>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -6031,8 +5968,12 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
+      <c r="A2" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B2" s="36" t="s">
+        <v>29</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -6043,8 +5984,12 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
+      <c r="A3" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>143</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -6055,8 +6000,12 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B4" s="38" t="s">
+        <v>145</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -6067,8 +6016,12 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3"/>
+      <c r="A5" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B5" s="39" t="s">
+        <v>145</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
       <c r="F5" s="3"/>
@@ -6079,8 +6032,12 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
+      <c r="A6" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B6" s="40" t="s">
+        <v>104</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="1"/>
       <c r="F6" s="3"/>
@@ -6091,8 +6048,12 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
+      <c r="A7" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>148</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="1"/>
       <c r="F7" s="3"/>
@@ -6103,8 +6064,12 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3"/>
+      <c r="A8" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>145</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="3"/>
@@ -6115,8 +6080,12 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
+      <c r="A9" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>127</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="3"/>
@@ -6127,8 +6096,12 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
+      <c r="A10" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>152</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="3"/>
@@ -6139,8 +6112,12 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
+      <c r="A11" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B11" s="45" t="s">
+        <v>109</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
       <c r="F11" s="3"/>
@@ -6151,8 +6128,12 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="3"/>
+      <c r="A12" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>111</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="1"/>
       <c r="F12" s="3"/>
@@ -6163,8 +6144,12 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
+      <c r="A13" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>153</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="1"/>
       <c r="F13" s="3"/>
@@ -6175,8 +6160,12 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3"/>
+      <c r="A14" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>152</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
       <c r="F14" s="3"/>
@@ -6187,8 +6176,12 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3"/>
+      <c r="A15" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>115</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
       <c r="F15" s="3"/>
@@ -6199,8 +6192,12 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
+      <c r="A16" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B16" s="50" t="s">
+        <v>117</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="3"/>
@@ -6211,8 +6208,12 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3"/>
+      <c r="A17" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B17" s="51" t="s">
+        <v>119</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
       <c r="F17" s="3"/>
@@ -6223,8 +6224,12 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3"/>
+      <c r="A18" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>121</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
       <c r="F18" s="3"/>
@@ -6235,8 +6240,12 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3"/>
+      <c r="A19" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B19" s="53" t="s">
+        <v>123</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="1"/>
       <c r="F19" s="3"/>
@@ -6247,8 +6256,12 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3"/>
+      <c r="A20" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B20" s="54" t="s">
+        <v>152</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="1"/>
       <c r="F20" s="3"/>
@@ -6259,8 +6272,12 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3"/>
+      <c r="A21" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B21" s="55" t="s">
+        <v>125</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="1"/>
       <c r="F21" s="3"/>
@@ -6271,8 +6288,12 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3"/>
+      <c r="A22" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B22" s="56" t="s">
+        <v>127</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="1"/>
       <c r="F22" s="3"/>
@@ -6283,8 +6304,12 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3"/>
+      <c r="A23" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>157</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
       <c r="F23" s="3"/>
@@ -6295,8 +6320,12 @@
       <c r="L23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3"/>
+      <c r="A24" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B24" s="58" t="s">
+        <v>158</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="1"/>
       <c r="F24" s="3"/>
@@ -6307,8 +6336,12 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="3"/>
+      <c r="A25" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B25" s="59" t="s">
+        <v>160</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="1"/>
       <c r="F25" s="3"/>
@@ -6319,8 +6352,12 @@
       <c r="L25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="3"/>
+      <c r="A26" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>129</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="1"/>
       <c r="F26" s="3"/>
@@ -6331,8 +6368,12 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="3"/>
+      <c r="A27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B27" s="61" t="s">
+        <v>79</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="1"/>
       <c r="F27" s="3"/>
@@ -6343,8 +6384,12 @@
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3"/>
+      <c r="A28" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B28" s="62" t="s">
+        <v>132</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="1"/>
       <c r="F28" s="3"/>
@@ -6355,8 +6400,12 @@
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="3"/>
+      <c r="A29" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B29" s="63" t="s">
+        <v>134</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="1"/>
       <c r="F29" s="3"/>
@@ -6367,8 +6416,12 @@
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3"/>
+      <c r="A30" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>136</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="E30" s="1"/>
       <c r="F30" s="3"/>
@@ -6379,8 +6432,12 @@
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="3"/>
+      <c r="A31" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B31" s="65" t="s">
+        <v>97</v>
+      </c>
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
       <c r="F31" s="3"/>
@@ -8085,8 +8142,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="B1" s="3"/>
+      <c r="A1" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B1" s="66" t="s">
+        <v>106</v>
+      </c>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -8097,8 +8158,12 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
+      <c r="A2" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B2" s="67" t="s">
+        <v>29</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -8109,8 +8174,12 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
+      <c r="A3" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>143</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -8121,8 +8190,12 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B4" s="69" t="s">
+        <v>145</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -8133,8 +8206,12 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3"/>
+      <c r="A5" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B5" s="70" t="s">
+        <v>145</v>
+      </c>
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
       <c r="F5" s="3"/>
@@ -8145,8 +8222,12 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3"/>
+      <c r="A6" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B6" s="71" t="s">
+        <v>104</v>
+      </c>
       <c r="D6" s="3"/>
       <c r="E6" s="1"/>
       <c r="F6" s="3"/>
@@ -8157,8 +8238,12 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3"/>
+      <c r="A7" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>148</v>
+      </c>
       <c r="D7" s="3"/>
       <c r="E7" s="1"/>
       <c r="F7" s="3"/>
@@ -8169,8 +8254,12 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3"/>
+      <c r="A8" t="s" s="0">
+        <v>149</v>
+      </c>
+      <c r="B8" s="73" t="s">
+        <v>145</v>
+      </c>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="3"/>
@@ -8181,8 +8270,12 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3"/>
+      <c r="A9" t="s" s="0">
+        <v>150</v>
+      </c>
+      <c r="B9" s="74" t="s">
+        <v>127</v>
+      </c>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="3"/>
@@ -8193,8 +8286,12 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3"/>
+      <c r="A10" t="s" s="0">
+        <v>151</v>
+      </c>
+      <c r="B10" s="75" t="s">
+        <v>152</v>
+      </c>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="3"/>
@@ -8205,8 +8302,12 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3"/>
+      <c r="A11" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B11" s="76" t="s">
+        <v>109</v>
+      </c>
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
       <c r="F11" s="3"/>
@@ -8217,8 +8318,12 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="3"/>
+      <c r="A12" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B12" s="77" t="s">
+        <v>111</v>
+      </c>
       <c r="D12" s="3"/>
       <c r="E12" s="1"/>
       <c r="F12" s="3"/>
@@ -8229,8 +8334,12 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3"/>
+      <c r="A13" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>153</v>
+      </c>
       <c r="D13" s="3"/>
       <c r="E13" s="1"/>
       <c r="F13" s="3"/>
@@ -8241,8 +8350,12 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3"/>
+      <c r="A14" t="s" s="0">
+        <v>154</v>
+      </c>
+      <c r="B14" s="79" t="s">
+        <v>152</v>
+      </c>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
       <c r="F14" s="3"/>
@@ -8253,8 +8366,12 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3"/>
+      <c r="A15" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B15" s="80" t="s">
+        <v>115</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
       <c r="F15" s="3"/>
@@ -8265,8 +8382,12 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3"/>
+      <c r="A16" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B16" s="81" t="s">
+        <v>117</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="3"/>
@@ -8277,8 +8398,12 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3"/>
+      <c r="A17" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B17" s="82" t="s">
+        <v>119</v>
+      </c>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
       <c r="F17" s="3"/>
@@ -8289,8 +8414,12 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3"/>
+      <c r="A18" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="B18" s="83" t="s">
+        <v>121</v>
+      </c>
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
       <c r="F18" s="3"/>
@@ -8301,8 +8430,12 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3"/>
+      <c r="A19" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B19" s="84" t="s">
+        <v>123</v>
+      </c>
       <c r="D19" s="3"/>
       <c r="E19" s="1"/>
       <c r="F19" s="3"/>
@@ -8313,8 +8446,12 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3"/>
+      <c r="A20" t="s" s="0">
+        <v>155</v>
+      </c>
+      <c r="B20" s="85" t="s">
+        <v>152</v>
+      </c>
       <c r="D20" s="3"/>
       <c r="E20" s="1"/>
       <c r="F20" s="3"/>
@@ -8325,8 +8462,12 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3"/>
+      <c r="A21" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B21" s="86" t="s">
+        <v>125</v>
+      </c>
       <c r="D21" s="3"/>
       <c r="E21" s="1"/>
       <c r="F21" s="3"/>
@@ -8337,8 +8478,12 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3"/>
+      <c r="A22" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B22" s="87" t="s">
+        <v>127</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="1"/>
       <c r="F22" s="3"/>
@@ -8349,8 +8494,12 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3"/>
+      <c r="A23" t="s" s="0">
+        <v>156</v>
+      </c>
+      <c r="B23" s="88" t="s">
+        <v>157</v>
+      </c>
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
       <c r="F23" s="3"/>
@@ -8361,8 +8510,12 @@
       <c r="L23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3"/>
+      <c r="A24" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B24" s="89" t="s">
+        <v>158</v>
+      </c>
       <c r="D24" s="3"/>
       <c r="E24" s="1"/>
       <c r="F24" s="3"/>
@@ -8373,8 +8526,12 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" s="1"/>
-      <c r="B25" s="3"/>
+      <c r="A25" t="s" s="0">
+        <v>159</v>
+      </c>
+      <c r="B25" s="90" t="s">
+        <v>160</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="1"/>
       <c r="F25" s="3"/>
@@ -8385,8 +8542,12 @@
       <c r="L25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="1"/>
-      <c r="B26" s="3"/>
+      <c r="A26" t="s" s="0">
+        <v>161</v>
+      </c>
+      <c r="B26" s="91" t="s">
+        <v>129</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="1"/>
       <c r="F26" s="3"/>
@@ -8397,8 +8558,12 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="3"/>
+      <c r="A27" t="s" s="0">
+        <v>130</v>
+      </c>
+      <c r="B27" s="92" t="s">
+        <v>79</v>
+      </c>
       <c r="D27" s="3"/>
       <c r="E27" s="1"/>
       <c r="F27" s="3"/>
@@ -8409,8 +8574,12 @@
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3"/>
+      <c r="A28" t="s" s="0">
+        <v>131</v>
+      </c>
+      <c r="B28" s="93" t="s">
+        <v>132</v>
+      </c>
       <c r="D28" s="3"/>
       <c r="E28" s="1"/>
       <c r="F28" s="3"/>
@@ -8421,8 +8590,12 @@
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="1"/>
-      <c r="B29" s="3"/>
+      <c r="A29" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B29" s="94" t="s">
+        <v>134</v>
+      </c>
       <c r="D29" s="3"/>
       <c r="E29" s="1"/>
       <c r="F29" s="3"/>
@@ -8433,8 +8606,12 @@
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3"/>
+      <c r="A30" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B30" s="95" t="s">
+        <v>136</v>
+      </c>
       <c r="D30" s="3"/>
       <c r="E30" s="1"/>
       <c r="F30" s="3"/>
@@ -8445,8 +8622,12 @@
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" s="1"/>
-      <c r="B31" s="3"/>
+      <c r="A31" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B31" s="96" t="s">
+        <v>97</v>
+      </c>
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
       <c r="F31" s="3"/>
@@ -8457,8 +8638,12 @@
       <c r="L31" s="3"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="1"/>
-      <c r="B32" s="3"/>
+      <c r="A32" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B32" s="97" t="s">
+        <v>139</v>
+      </c>
       <c r="D32" s="3"/>
       <c r="E32" s="1"/>
       <c r="F32" s="3"/>
@@ -8469,8 +8654,12 @@
       <c r="L32" s="3"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="3"/>
+      <c r="A33" t="s" s="0">
+        <v>165</v>
+      </c>
+      <c r="B33" s="98" t="s">
+        <v>141</v>
+      </c>
       <c r="D33" s="3"/>
       <c r="E33" s="1"/>
       <c r="F33" s="3"/>
@@ -10145,10 +10334,10 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -10156,10 +10345,10 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -10167,10 +10356,10 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -10178,10 +10367,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -10210,16 +10399,16 @@
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -10227,16 +10416,16 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -10244,16 +10433,16 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -10261,16 +10450,16 @@
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -10278,16 +10467,16 @@
     </row>
     <row r="5" ht="14.25" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -10295,16 +10484,16 @@
     </row>
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="9" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>3</v>
@@ -10329,16 +10518,16 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -10346,16 +10535,16 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>3</v>
@@ -10363,16 +10552,16 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>3</v>
@@ -10380,16 +10569,16 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>3</v>
@@ -10397,16 +10586,16 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>3</v>
@@ -10433,10 +10622,10 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -10444,10 +10633,10 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -10455,10 +10644,10 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -10466,10 +10655,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -10477,10 +10666,10 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -10488,10 +10677,10 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -10499,10 +10688,10 @@
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -10510,10 +10699,10 @@
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -10521,10 +10710,10 @@
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -10532,10 +10721,10 @@
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -10543,10 +10732,10 @@
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>3</v>
@@ -10554,10 +10743,10 @@
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -10565,10 +10754,10 @@
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -10576,10 +10765,10 @@
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -10587,10 +10776,10 @@
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -10617,10 +10806,10 @@
   <sheetData>
     <row r="1" ht="15" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -10628,10 +10817,10 @@
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -10639,10 +10828,10 @@
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -10650,10 +10839,10 @@
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -10661,10 +10850,10 @@
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -10672,10 +10861,10 @@
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -25,14 +25,13 @@
     <sheet name="AddMaxHighSchoolTest" sheetId="13" r:id="rId13"/>
     <sheet name="overAllAcademicsTest" sheetId="14" r:id="rId14"/>
     <sheet name="CollegeUniversitiesTest" sheetId="15" r:id="rId15"/>
-    <sheet name="Mismatch_01_valid_vs_Revie" r:id="rId19" sheetId="16"/>
   </sheets>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>TCID</t>
   </si>
@@ -343,12 +342,6 @@
     <t>Test Degree</t>
   </si>
   <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>5382521@test.asu.edu</t>
-  </si>
-  <si>
     <t>Legal name</t>
   </si>
   <si>
@@ -358,435 +351,10 @@
     <t>Preferred first name</t>
   </si>
   <si>
-    <t>Legal sex</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Primary language spoken at home</t>
-  </si>
-  <si>
-    <t>Chhattisgarhi</t>
-  </si>
-  <si>
-    <t>Home address</t>
-  </si>
-  <si>
-    <t>Test Address Line I Test Address Line II
-Test City,Arizona,United States
-United States
-Afghanistan
-Aland Islands
-Albania
-Algeria
-American Samoa
-Andorra
-Angola
-Anguilla
-Antarctica
-Antigua and Barbuda
-Argentina
-Armenia
-Aruba
-Australia
-Austria
-Azerbaijan
-Bahamas, The
-Bahrain
-Bangladesh
-Barbados
-Belarus
-Belgium
-Belize
-Benin
-Bermuda
-Bhutan
-Bolivia
-Bonaire, Sint Eustatius &amp; Saba
-Bosnia and Herzegovina
-Botswana
-Bouvet Island
-Brazil
-British Indian Ocean Territory
-British Virgin Islands
-Brunei
-Bulgaria
-Burkina Faso
-Burma
-Burundi
-Cambodia
-Cameroon
-Canada
-Cape Verde
-Cayman Islands
-Central African Republic
-Chad
-Chile
-China
-Christmas Island
-Cocos (Keeling) Islands
-Colombia
-Comoros
-Congo
-Congo, Democratic Republic of
-Cook Islands
-Costa Rica
-Cote D'Ivoire
-Croatia
-Cuba
-Curacao
-Cyprus
-Czech Republic
-Denmark
-Djibouti
-Dominica
-Dominican Republic
-Ecuador
-Egypt
-El Salvador
-Equatorial Guinea
-Eritrea
-Estonia
-Eswatini
-Ethiopia
-Falkland Islands (Malvinas)
-Faroe Islands
-Fiji
-Finland
-France
-French Guiana
-French Polynesia
-French Southern &amp; Antarc Lands
-Gabon
-Gambia, The
-Georgia
-Germany
-Ghana
-Gibraltar
-Greece
-Greenland
-Grenada
-Guadeloupe
-Guam
-Guatemala
-Guernsey
-Guinea
-Guinea-Bissau
-Guyana
-Haiti
-Heard and McDonald Islands
-Honduras
-Hong Kong
-Hungary
-Iceland
-India
-Indonesia
-Iran
-Iraq
-Ireland
-Isle of Man
-Israel
-Italy
-Jamaica
-Japan
-Jersey
-Jordan
-Kazakhstan
-Kenya
-Kiribati
-Kosovo
-Kuwait
-Kyrgyzstan
-Laos
-Latvia
-Lebanon
-Lesotho
-Liberia
-Libya
-Liechtenstein
-Lithuania
-Luxembourg
-Macau
-Madagascar
-Malawi
-Malaysia
-Maldives
-Mali
-Malta
-Marshall Islands
-Martinique
-Mauritania
-Mauritius
-Mayotte
-Mexico
-Micronesia, Federated States
-Moldova
-Monaco
-Mongolia
-Montenegro
-Montserrat
-Morocco
-Mozambique
-Namibia
-Nauru
-Nepal
-Netherlands
-Netherlands Antilles
-New Caledonia
-New Zealand
-Nicaragua
-Niger
-Nigeria
-Niue
-Norfolk Island
-North Korea
-Northern Mariana Islands
-Norway
-Oman
-Pakistan
-Palau
-Palestinian Territory, Occupie
-Panama
-Papua New Guinea
-Paraguay
-Peru
-Philippines
-Pitcairn Islands
-Poland
-Portugal
-Puerto Rico
-Qatar
-Republic of North Macedonia
-Reunion
-Romania
-Russia
-Rwanda
-Saint Barthelemy
-Saint Helena
-Saint Kitts and Nevis
-Saint Lucia
-Saint Martin
-Saint Pierre and Miquelon
-Saint Vincent &amp; the Grenadines
-Samoa
-San Marino
-Sao Tome and Principe
-Saudi Arabia
-Senegal
-Serbia
-Seychelles
-Sierra Leone
-Singapore
-Sint Maarten (Dutch part)
-Slovakia
-Slovenia
-Solomon Islands
-Somalia
-South Africa
-South Georgia &amp; S Sandwich Is
-South Korea
-South Sudan
-Spain
-Spratly Islands
-Sri Lanka
-Sudan
-Suriname
-Svalbard and Jan Mayen
-Sweden
-Switzerland
-Syria
-Taiwan
-Tajikistan
-Tanzania
-Thailand
-Timor-Leste
-Togo
-Tokelau
-Tonga
-Trinidad and Tobago
-Tunisia
-Turkey
-Turkmenistan
-Turks and Caicos Islands
-Tuvalu
-US Misc Pacific Islands
-Uganda
-Ukraine
-United Arab Emirates
-United Kingdom
-Uruguay
-Uzbekistan
-Vanuatu
-Vatican City
-Venezuela
-Vietnam
-Virgin Islands
-Wallis and Futuna Islands
-Western Sahara
-Yemen
-Yugoslavia
-Zambia
-Zimbabwe
-12345-678910</t>
-  </si>
-  <si>
-    <t>U.S. citizenship</t>
-  </si>
-  <si>
-    <t>I am a U.S. citizen</t>
-  </si>
-  <si>
-    <t>Country of citizenship</t>
-  </si>
-  <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Country of birth</t>
-  </si>
-  <si>
-    <t>South Korea</t>
-  </si>
-  <si>
-    <t>Social Security Number</t>
-  </si>
-  <si>
-    <t>*********</t>
-  </si>
-  <si>
-    <t>Previous ASU affiliation</t>
-  </si>
-  <si>
-    <t>I have never been affiliated with Arizona State University</t>
-  </si>
-  <si>
-    <t>Military status</t>
-  </si>
-  <si>
-    <t>None of these options apply to me</t>
-  </si>
-  <si>
-    <t>Do you plan to use an education benefit or scholarship through an employer, corporation, foundation or other ASU education partner?</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Graduating school </t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>High school name</t>
-  </si>
-  <si>
-    <t>Name on transcript</t>
-  </si>
-  <si>
-    <t>Test FN Test LN</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>Test City, BS, GNQ</t>
-  </si>
-  <si>
-    <t>Graduation date</t>
-  </si>
-  <si>
-    <t>July, 2027</t>
-  </si>
-  <si>
-    <t>Transfer credits to ASU</t>
-  </si>
-  <si>
-    <t>Begin by selecting the state you consider to be your permanent home.</t>
-  </si>
-  <si>
-    <t>Outside the U.S. or Not Listed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In which state do your parent(s) or legal guardian(s) currently live? </t>
-  </si>
-  <si>
-    <t>New Hampshire</t>
-  </si>
-  <si>
     <t>Date of birth</t>
   </si>
   <si>
-    <t>November 11, 2010</t>
-  </si>
-  <si>
-    <t>Pronouns</t>
-  </si>
-  <si>
-    <t>No data has been entered</t>
-  </si>
-  <si>
-    <t>Gender identity</t>
-  </si>
-  <si>
-    <t>Phone</t>
-  </si>
-  <si>
-    <t>+1 (234) 567-6543</t>
-  </si>
-  <si>
-    <t>Mobile phone</t>
-  </si>
-  <si>
-    <t>Mobile SMS</t>
-  </si>
-  <si>
-    <t>Former name(s)</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <t>Test Address Line I Test Address Line II
-Test City,Arizona,United States
-12345-678910</t>
-  </si>
-  <si>
-    <t>Ethnic/racial background</t>
-  </si>
-  <si>
-    <t>Affiliate ID</t>
-  </si>
-  <si>
-    <t>Program</t>
-  </si>
-  <si>
-    <t>Nondegree</t>
-  </si>
-  <si>
-    <t>ASU Online</t>
-  </si>
-  <si>
-    <t>Starting term</t>
-  </si>
-  <si>
-    <t>Fall 2025 - (Session B)</t>
-  </si>
-  <si>
-    <t>Graduating school</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Value Sheet 1</t>
-  </si>
-  <si>
-    <t>Value Sheet 2</t>
-  </si>
-  <si>
-    <t>In which state do your parent(s) or legal guardian(s) currently live?</t>
+    <t>November 13, 1964</t>
   </si>
 </sst>
 </file>
@@ -865,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -888,252 +456,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
@@ -3673,38 +2995,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="0">
-        <v>162</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>113</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>153</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:L1000"/>
@@ -3721,12 +3011,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>104</v>
-      </c>
+      <c r="B1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -3737,10 +3022,10 @@
     </row>
     <row r="2" ht="14.25" customHeight="1">
       <c r="A2" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>106</v>
+        <v>103</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
@@ -3751,9 +3036,9 @@
     </row>
     <row r="3" ht="14.25" customHeight="1">
       <c r="A3" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="B3" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>29</v>
       </c>
       <c r="D3" s="3"/>
@@ -3764,8 +3049,12 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>107</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -3803,12 +3092,7 @@
       <c r="H7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>109</v>
-      </c>
+      <c r="B8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="3"/>
@@ -3817,12 +3101,7 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>111</v>
-      </c>
+      <c r="B9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="3"/>
@@ -3831,12 +3110,7 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="137.25" customHeight="1">
-      <c r="A10" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>113</v>
-      </c>
+      <c r="B10" s="4"/>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="3"/>
@@ -3878,12 +3152,8 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" t="s" s="0">
-        <v>114</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>115</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
       <c r="F14" s="3"/>
@@ -3892,12 +3162,8 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>117</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
       <c r="F15" s="3"/>
@@ -3906,12 +3172,8 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>119</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="3"/>
@@ -3920,12 +3182,8 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" t="s" s="0">
-        <v>120</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>121</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
       <c r="F17" s="3"/>
@@ -3981,12 +3239,8 @@
       <c r="B26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>123</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="1"/>
       <c r="F27" s="3"/>
@@ -4005,12 +3259,8 @@
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>125</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="1"/>
       <c r="F29" s="3"/>
@@ -4046,12 +3296,8 @@
       <c r="L32" s="3"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>127</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="1"/>
       <c r="F33" s="3"/>
@@ -4179,12 +3425,8 @@
       <c r="L44" s="3"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" t="s" s="0">
-        <v>128</v>
-      </c>
-      <c r="B45" s="27" t="s">
-        <v>129</v>
-      </c>
+      <c r="A45" s="1"/>
+      <c r="B45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="1"/>
       <c r="F45" s="3"/>
@@ -4195,12 +3437,8 @@
       <c r="L45" s="3"/>
     </row>
     <row r="46" ht="14.25" customHeight="1">
-      <c r="A46" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B46" s="28" t="s">
-        <v>79</v>
-      </c>
+      <c r="A46" s="1"/>
+      <c r="B46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="1"/>
       <c r="F46" s="3"/>
@@ -4211,12 +3449,8 @@
       <c r="L46" s="3"/>
     </row>
     <row r="47" ht="14.25" customHeight="1">
-      <c r="A47" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="B47" s="29" t="s">
-        <v>132</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="B47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="1"/>
       <c r="F47" s="3"/>
@@ -4227,12 +3461,8 @@
       <c r="L47" s="3"/>
     </row>
     <row r="48" ht="14.25" customHeight="1">
-      <c r="A48" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="B48" s="30" t="s">
-        <v>134</v>
-      </c>
+      <c r="A48" s="1"/>
+      <c r="B48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="1"/>
       <c r="F48" s="3"/>
@@ -4243,12 +3473,8 @@
       <c r="L48" s="3"/>
     </row>
     <row r="49" ht="14.25" customHeight="1">
-      <c r="A49" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>136</v>
-      </c>
+      <c r="A49" s="1"/>
+      <c r="B49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="1"/>
       <c r="F49" s="3"/>
@@ -4259,12 +3485,8 @@
       <c r="L49" s="3"/>
     </row>
     <row r="50" ht="14.25" customHeight="1">
-      <c r="A50" t="s" s="0">
-        <v>137</v>
-      </c>
-      <c r="B50" s="32" t="s">
-        <v>97</v>
-      </c>
+      <c r="A50" s="1"/>
+      <c r="B50" s="3"/>
       <c r="D50" s="3"/>
       <c r="H50" s="3"/>
     </row>
@@ -4755,12 +3977,8 @@
       <c r="F125" s="3"/>
     </row>
     <row r="126" ht="14.25" customHeight="1">
-      <c r="A126" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="B126" s="33" t="s">
-        <v>139</v>
-      </c>
+      <c r="A126" s="1"/>
+      <c r="B126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="1"/>
       <c r="F126" s="3"/>
@@ -5022,12 +4240,7 @@
       <c r="F177" s="3"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c r="A178" t="s" s="0">
-        <v>140</v>
-      </c>
-      <c r="B178" s="34" t="s">
-        <v>141</v>
-      </c>
+      <c r="B178" s="3"/>
       <c r="D178" s="3"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -5952,12 +5165,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B1" s="35" t="s">
-        <v>106</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -5968,12 +5177,8 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="B2" s="36" t="s">
-        <v>29</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -5984,12 +5189,8 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>143</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -6000,12 +5201,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="B4" s="38" t="s">
-        <v>145</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -6016,12 +5213,8 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B5" s="39" t="s">
-        <v>145</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
       <c r="F5" s="3"/>
@@ -6032,12 +5225,8 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B6" s="40" t="s">
-        <v>104</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1"/>
       <c r="F6" s="3"/>
@@ -6048,12 +5237,8 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" t="s" s="0">
-        <v>147</v>
-      </c>
-      <c r="B7" s="41" t="s">
-        <v>148</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1"/>
       <c r="F7" s="3"/>
@@ -6064,12 +5249,8 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>145</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="3"/>
@@ -6080,12 +5261,8 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="B9" s="43" t="s">
-        <v>127</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="3"/>
@@ -6096,12 +5273,8 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>152</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="3"/>
@@ -6112,12 +5285,8 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>109</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
       <c r="F11" s="3"/>
@@ -6128,12 +5297,8 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>111</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="1"/>
       <c r="F12" s="3"/>
@@ -6144,12 +5309,8 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" ht="33" customHeight="1">
-      <c r="A13" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>153</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="1"/>
       <c r="F13" s="3"/>
@@ -6160,12 +5321,8 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B14" s="48" t="s">
-        <v>152</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
       <c r="F14" s="3"/>
@@ -6176,12 +5333,8 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" t="s" s="0">
-        <v>114</v>
-      </c>
-      <c r="B15" s="49" t="s">
-        <v>115</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
       <c r="F15" s="3"/>
@@ -6192,12 +5345,8 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>117</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="3"/>
@@ -6208,12 +5357,8 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>119</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
       <c r="F17" s="3"/>
@@ -6224,12 +5369,8 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" t="s" s="0">
-        <v>120</v>
-      </c>
-      <c r="B18" s="52" t="s">
-        <v>121</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
       <c r="F18" s="3"/>
@@ -6240,12 +5381,8 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B19" s="53" t="s">
-        <v>123</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="1"/>
       <c r="F19" s="3"/>
@@ -6256,12 +5393,8 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" t="s" s="0">
-        <v>155</v>
-      </c>
-      <c r="B20" s="54" t="s">
-        <v>152</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="1"/>
       <c r="F20" s="3"/>
@@ -6272,12 +5405,8 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="B21" s="55" t="s">
-        <v>125</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="1"/>
       <c r="F21" s="3"/>
@@ -6288,12 +5417,8 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="B22" s="56" t="s">
-        <v>127</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="1"/>
       <c r="F22" s="3"/>
@@ -6304,12 +5429,8 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="B23" s="57" t="s">
-        <v>157</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
       <c r="F23" s="3"/>
@@ -6320,12 +5441,8 @@
       <c r="L23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="B24" s="58" t="s">
-        <v>158</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="1"/>
       <c r="F24" s="3"/>
@@ -6336,12 +5453,8 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="B25" s="59" t="s">
-        <v>160</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="1"/>
       <c r="F25" s="3"/>
@@ -6352,12 +5465,8 @@
       <c r="L25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" t="s" s="0">
-        <v>161</v>
-      </c>
-      <c r="B26" s="60" t="s">
-        <v>129</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="1"/>
       <c r="F26" s="3"/>
@@ -6368,12 +5477,8 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B27" s="61" t="s">
-        <v>79</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="1"/>
       <c r="F27" s="3"/>
@@ -6384,12 +5489,8 @@
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="B28" s="62" t="s">
-        <v>132</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="1"/>
       <c r="F28" s="3"/>
@@ -6400,12 +5501,8 @@
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="B29" s="63" t="s">
-        <v>134</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="1"/>
       <c r="F29" s="3"/>
@@ -6416,12 +5513,8 @@
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="B30" s="64" t="s">
-        <v>136</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="1"/>
       <c r="F30" s="3"/>
@@ -6432,12 +5525,8 @@
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" t="s" s="0">
-        <v>137</v>
-      </c>
-      <c r="B31" s="65" t="s">
-        <v>97</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
       <c r="F31" s="3"/>
@@ -8142,12 +7231,8 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B1" s="66" t="s">
-        <v>106</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -8158,12 +7243,8 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" t="s" s="0">
-        <v>107</v>
-      </c>
-      <c r="B2" s="67" t="s">
-        <v>29</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -8174,12 +7255,8 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" t="s" s="0">
-        <v>142</v>
-      </c>
-      <c r="B3" s="68" t="s">
-        <v>143</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -8190,12 +7267,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>144</v>
-      </c>
-      <c r="B4" s="69" t="s">
-        <v>145</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -8206,12 +7279,8 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" ht="14.25" customHeight="1">
-      <c r="A5" t="s" s="0">
-        <v>146</v>
-      </c>
-      <c r="B5" s="70" t="s">
-        <v>145</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="3"/>
       <c r="D5" s="3"/>
       <c r="E5" s="1"/>
       <c r="F5" s="3"/>
@@ -8222,12 +7291,8 @@
       <c r="L5" s="3"/>
     </row>
     <row r="6" ht="14.25" customHeight="1">
-      <c r="A6" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>104</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="1"/>
       <c r="F6" s="3"/>
@@ -8238,12 +7303,8 @@
       <c r="L6" s="3"/>
     </row>
     <row r="7" ht="14.25" customHeight="1">
-      <c r="A7" t="s" s="0">
-        <v>147</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>148</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="1"/>
       <c r="F7" s="3"/>
@@ -8254,12 +7315,8 @@
       <c r="L7" s="3"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" t="s" s="0">
-        <v>149</v>
-      </c>
-      <c r="B8" s="73" t="s">
-        <v>145</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="3"/>
       <c r="D8" s="3"/>
       <c r="E8" s="1"/>
       <c r="F8" s="3"/>
@@ -8270,12 +7327,8 @@
       <c r="L8" s="3"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
-      <c r="A9" t="s" s="0">
-        <v>150</v>
-      </c>
-      <c r="B9" s="74" t="s">
-        <v>127</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="1"/>
       <c r="F9" s="3"/>
@@ -8286,12 +7339,8 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" ht="14.25" customHeight="1">
-      <c r="A10" t="s" s="0">
-        <v>151</v>
-      </c>
-      <c r="B10" s="75" t="s">
-        <v>152</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="1"/>
       <c r="F10" s="3"/>
@@ -8302,12 +7351,8 @@
       <c r="L10" s="3"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
-      <c r="A11" t="s" s="0">
-        <v>108</v>
-      </c>
-      <c r="B11" s="76" t="s">
-        <v>109</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="1"/>
       <c r="F11" s="3"/>
@@ -8318,12 +7363,8 @@
       <c r="L11" s="3"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
-      <c r="A12" t="s" s="0">
-        <v>110</v>
-      </c>
-      <c r="B12" s="77" t="s">
-        <v>111</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="1"/>
       <c r="F12" s="3"/>
@@ -8334,12 +7375,8 @@
       <c r="L12" s="3"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
-      <c r="A13" t="s" s="0">
-        <v>112</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>153</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="1"/>
       <c r="F13" s="3"/>
@@ -8350,12 +7387,8 @@
       <c r="L13" s="3"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" t="s" s="0">
-        <v>154</v>
-      </c>
-      <c r="B14" s="79" t="s">
-        <v>152</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="1"/>
       <c r="F14" s="3"/>
@@ -8366,12 +7399,8 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" t="s" s="0">
-        <v>114</v>
-      </c>
-      <c r="B15" s="80" t="s">
-        <v>115</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="1"/>
       <c r="F15" s="3"/>
@@ -8382,12 +7411,8 @@
       <c r="L15" s="3"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" t="s" s="0">
-        <v>116</v>
-      </c>
-      <c r="B16" s="81" t="s">
-        <v>117</v>
-      </c>
+      <c r="A16" s="1"/>
+      <c r="B16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="1"/>
       <c r="F16" s="3"/>
@@ -8398,12 +7423,8 @@
       <c r="L16" s="3"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" t="s" s="0">
-        <v>118</v>
-      </c>
-      <c r="B17" s="82" t="s">
-        <v>119</v>
-      </c>
+      <c r="A17" s="1"/>
+      <c r="B17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="1"/>
       <c r="F17" s="3"/>
@@ -8414,12 +7435,8 @@
       <c r="L17" s="3"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" t="s" s="0">
-        <v>120</v>
-      </c>
-      <c r="B18" s="83" t="s">
-        <v>121</v>
-      </c>
+      <c r="A18" s="1"/>
+      <c r="B18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="1"/>
       <c r="F18" s="3"/>
@@ -8430,12 +7447,8 @@
       <c r="L18" s="3"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" t="s" s="0">
-        <v>122</v>
-      </c>
-      <c r="B19" s="84" t="s">
-        <v>123</v>
-      </c>
+      <c r="A19" s="1"/>
+      <c r="B19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="1"/>
       <c r="F19" s="3"/>
@@ -8446,12 +7459,8 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" t="s" s="0">
-        <v>155</v>
-      </c>
-      <c r="B20" s="85" t="s">
-        <v>152</v>
-      </c>
+      <c r="A20" s="1"/>
+      <c r="B20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="1"/>
       <c r="F20" s="3"/>
@@ -8462,12 +7471,8 @@
       <c r="L20" s="3"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" t="s" s="0">
-        <v>124</v>
-      </c>
-      <c r="B21" s="86" t="s">
-        <v>125</v>
-      </c>
+      <c r="A21" s="1"/>
+      <c r="B21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="1"/>
       <c r="F21" s="3"/>
@@ -8478,12 +7483,8 @@
       <c r="L21" s="3"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" t="s" s="0">
-        <v>126</v>
-      </c>
-      <c r="B22" s="87" t="s">
-        <v>127</v>
-      </c>
+      <c r="A22" s="1"/>
+      <c r="B22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="1"/>
       <c r="F22" s="3"/>
@@ -8494,12 +7495,8 @@
       <c r="L22" s="3"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" t="s" s="0">
-        <v>156</v>
-      </c>
-      <c r="B23" s="88" t="s">
-        <v>157</v>
-      </c>
+      <c r="A23" s="1"/>
+      <c r="B23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="1"/>
       <c r="F23" s="3"/>
@@ -8510,12 +7507,8 @@
       <c r="L23" s="3"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="B24" s="89" t="s">
-        <v>158</v>
-      </c>
+      <c r="A24" s="1"/>
+      <c r="B24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="1"/>
       <c r="F24" s="3"/>
@@ -8526,12 +7519,8 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="A25" t="s" s="0">
-        <v>159</v>
-      </c>
-      <c r="B25" s="90" t="s">
-        <v>160</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="1"/>
       <c r="F25" s="3"/>
@@ -8542,12 +7531,8 @@
       <c r="L25" s="3"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" t="s" s="0">
-        <v>161</v>
-      </c>
-      <c r="B26" s="91" t="s">
-        <v>129</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="1"/>
       <c r="F26" s="3"/>
@@ -8558,12 +7543,8 @@
       <c r="L26" s="3"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" t="s" s="0">
-        <v>130</v>
-      </c>
-      <c r="B27" s="92" t="s">
-        <v>79</v>
-      </c>
+      <c r="A27" s="1"/>
+      <c r="B27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="1"/>
       <c r="F27" s="3"/>
@@ -8574,12 +7555,8 @@
       <c r="L27" s="3"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" t="s" s="0">
-        <v>131</v>
-      </c>
-      <c r="B28" s="93" t="s">
-        <v>132</v>
-      </c>
+      <c r="A28" s="1"/>
+      <c r="B28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="1"/>
       <c r="F28" s="3"/>
@@ -8590,12 +7567,8 @@
       <c r="L28" s="3"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" t="s" s="0">
-        <v>133</v>
-      </c>
-      <c r="B29" s="94" t="s">
-        <v>134</v>
-      </c>
+      <c r="A29" s="1"/>
+      <c r="B29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="1"/>
       <c r="F29" s="3"/>
@@ -8606,12 +7579,8 @@
       <c r="L29" s="3"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="A30" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="B30" s="95" t="s">
-        <v>136</v>
-      </c>
+      <c r="A30" s="1"/>
+      <c r="B30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="1"/>
       <c r="F30" s="3"/>
@@ -8622,12 +7591,8 @@
       <c r="L30" s="3"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="A31" t="s" s="0">
-        <v>137</v>
-      </c>
-      <c r="B31" s="96" t="s">
-        <v>97</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="1"/>
       <c r="F31" s="3"/>
@@ -8638,12 +7603,8 @@
       <c r="L31" s="3"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" t="s" s="0">
-        <v>138</v>
-      </c>
-      <c r="B32" s="97" t="s">
-        <v>139</v>
-      </c>
+      <c r="A32" s="1"/>
+      <c r="B32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="1"/>
       <c r="F32" s="3"/>
@@ -8654,12 +7615,8 @@
       <c r="L32" s="3"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" t="s" s="0">
-        <v>165</v>
-      </c>
-      <c r="B33" s="98" t="s">
-        <v>141</v>
-      </c>
+      <c r="A33" s="1"/>
+      <c r="B33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="1"/>
       <c r="F33" s="3"/>

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>TCID</t>
   </si>
@@ -340,28 +340,12 @@
   </si>
   <si>
     <t>Test Degree</t>
-  </si>
-  <si>
-    <t>Legal name</t>
-  </si>
-  <si>
-    <t>Test FN Automation MN Test LN</t>
-  </si>
-  <si>
-    <t>Preferred first name</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>November 13, 1964</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -433,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -456,15 +440,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,11 +648,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="24.57"/>
-    <col min="2" max="6" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="24.57" customWidth="1"/>
+    <col min="2" max="6" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2391,15 +2365,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="18.57"/>
-    <col min="7" max="7" customWidth="true" width="30.14"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18.57" customWidth="1"/>
+    <col min="7" max="7" width="30.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2491,14 +2464,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="14.43"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2572,14 +2544,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.14"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="41.43"/>
-    <col min="4" max="4" customWidth="true" width="34.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="27.14" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="41.43" customWidth="1"/>
+    <col min="4" max="4" width="34.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2644,10 +2615,9 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2831,10 +2801,9 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="4" customWidth="true" width="14.43"/>
+    <col min="1" max="4" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2928,14 +2897,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="31.0"/>
-    <col min="2" max="2" customWidth="true" width="27.43"/>
-    <col min="3" max="3" customWidth="true" width="51.0"/>
-    <col min="4" max="4" customWidth="true" width="22.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="27.43" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
+    <col min="4" max="4" width="22.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2997,17 +2965,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="36.86"/>
-    <col min="2" max="2" customWidth="true" width="41.14"/>
-    <col min="3" max="3" customWidth="true" width="20.43"/>
-    <col min="4" max="4" customWidth="true" width="20.14"/>
-    <col min="5" max="5" customWidth="true" width="31.43"/>
-    <col min="6" max="6" customWidth="true" width="24.43"/>
-    <col min="7" max="7" customWidth="true" width="26.71"/>
-    <col min="12" max="12" customWidth="true" width="40.71"/>
+    <col min="1" max="1" width="36.86" customWidth="1"/>
+    <col min="2" max="2" width="41.14" customWidth="1"/>
+    <col min="3" max="3" width="20.43" customWidth="1"/>
+    <col min="4" max="4" width="20.14" customWidth="1"/>
+    <col min="5" max="5" width="31.43" customWidth="1"/>
+    <col min="6" max="6" width="24.43" customWidth="1"/>
+    <col min="7" max="7" width="26.71" customWidth="1"/>
+    <col min="12" max="12" width="40.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -3021,12 +2988,8 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>104</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -3035,12 +2998,8 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -3049,12 +3008,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>107</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -5153,15 +5108,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="13.14"/>
-    <col min="2" max="2" customWidth="true" width="23.71"/>
-    <col min="3" max="3" customWidth="true" width="45.14"/>
-    <col min="4" max="4" customWidth="true" width="14.57"/>
-    <col min="5" max="5" customWidth="true" width="60.0"/>
-    <col min="6" max="6" customWidth="true" width="25.14"/>
+    <col min="1" max="1" width="13.14" customWidth="1"/>
+    <col min="2" max="2" width="23.71" customWidth="1"/>
+    <col min="3" max="3" width="45.14" customWidth="1"/>
+    <col min="4" max="4" width="14.57" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="25.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7219,15 +7173,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.29"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="24.57"/>
-    <col min="4" max="4" customWidth="true" width="27.57"/>
-    <col min="5" max="5" customWidth="true" width="25.29"/>
-    <col min="6" max="6" customWidth="true" width="33.57"/>
+    <col min="1" max="1" width="37.29" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="24.57" customWidth="1"/>
+    <col min="4" max="4" width="27.57" customWidth="1"/>
+    <col min="5" max="5" width="25.29" customWidth="1"/>
+    <col min="6" max="6" width="33.57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9281,12 +9234,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="14.14"/>
-    <col min="3" max="3" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="14.14" customWidth="1"/>
+    <col min="3" max="3" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9344,14 +9296,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="29.43"/>
-    <col min="2" max="2" customWidth="true" width="31.43"/>
-    <col min="3" max="3" customWidth="true" width="28.71"/>
-    <col min="4" max="4" customWidth="true" width="30.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="29.43" customWidth="1"/>
+    <col min="2" max="2" width="31.43" customWidth="1"/>
+    <col min="3" max="3" width="28.71" customWidth="1"/>
+    <col min="4" max="4" width="30.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9464,13 +9415,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="20.14"/>
-    <col min="3" max="4" customWidth="true" width="13.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="20.14" customWidth="1"/>
+    <col min="3" max="4" width="13.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9569,12 +9519,11 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.57"/>
-    <col min="2" max="2" customWidth="true" width="39.86"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="27.57" customWidth="1"/>
+    <col min="2" max="2" width="39.86" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9753,12 +9702,11 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="56.0"/>
-    <col min="2" max="2" customWidth="true" width="57.0"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>TCID</t>
   </si>
@@ -340,12 +340,28 @@
   </si>
   <si>
     <t>Test Degree</t>
+  </si>
+  <si>
+    <t>Legal name</t>
+  </si>
+  <si>
+    <t>Test FN Automation MN Test LN</t>
+  </si>
+  <si>
+    <t>Preferred first name</t>
+  </si>
+  <si>
+    <t>Date of birth</t>
+  </si>
+  <si>
+    <t>January 23, 1962</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -417,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -440,6 +456,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,10 +673,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="24.57" customWidth="1"/>
-    <col min="2" max="6" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="24.57"/>
+    <col min="2" max="6" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2365,14 +2391,15 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="22.29" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="18.57" customWidth="1"/>
-    <col min="7" max="7" width="30.14" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="38.29"/>
+    <col min="3" max="3" customWidth="true" width="34.0"/>
+    <col min="4" max="4" customWidth="true" width="22.29"/>
+    <col min="5" max="5" customWidth="true" width="30.0"/>
+    <col min="6" max="6" customWidth="true" width="18.57"/>
+    <col min="7" max="7" customWidth="true" width="30.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2464,13 +2491,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="22.29" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="14.43" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="38.29"/>
+    <col min="3" max="3" customWidth="true" width="34.0"/>
+    <col min="4" max="4" customWidth="true" width="22.29"/>
+    <col min="5" max="5" customWidth="true" width="30.0"/>
+    <col min="6" max="6" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2544,13 +2572,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.14" customWidth="1"/>
-    <col min="2" max="2" width="29.57" customWidth="1"/>
-    <col min="3" max="3" width="41.43" customWidth="1"/>
-    <col min="4" max="4" width="34.43" customWidth="1"/>
-    <col min="5" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.14"/>
+    <col min="2" max="2" customWidth="true" width="29.57"/>
+    <col min="3" max="3" customWidth="true" width="41.43"/>
+    <col min="4" max="4" customWidth="true" width="34.43"/>
+    <col min="5" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2615,9 +2644,10 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2801,9 +2831,10 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="14.43" customWidth="1"/>
+    <col min="1" max="4" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2897,13 +2928,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="27.43" customWidth="1"/>
-    <col min="3" max="3" width="51" customWidth="1"/>
-    <col min="4" max="4" width="22.43" customWidth="1"/>
-    <col min="5" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="31.0"/>
+    <col min="2" max="2" customWidth="true" width="27.43"/>
+    <col min="3" max="3" customWidth="true" width="51.0"/>
+    <col min="4" max="4" customWidth="true" width="22.43"/>
+    <col min="5" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2965,16 +2997,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="36.86" customWidth="1"/>
-    <col min="2" max="2" width="41.14" customWidth="1"/>
-    <col min="3" max="3" width="20.43" customWidth="1"/>
-    <col min="4" max="4" width="20.14" customWidth="1"/>
-    <col min="5" max="5" width="31.43" customWidth="1"/>
-    <col min="6" max="6" width="24.43" customWidth="1"/>
-    <col min="7" max="7" width="26.71" customWidth="1"/>
-    <col min="12" max="12" width="40.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="36.86"/>
+    <col min="2" max="2" customWidth="true" width="41.14"/>
+    <col min="3" max="3" customWidth="true" width="20.43"/>
+    <col min="4" max="4" customWidth="true" width="20.14"/>
+    <col min="5" max="5" customWidth="true" width="31.43"/>
+    <col min="6" max="6" customWidth="true" width="24.43"/>
+    <col min="7" max="7" customWidth="true" width="26.71"/>
+    <col min="12" max="12" customWidth="true" width="40.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -2988,8 +3021,12 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
+      <c r="A2" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -2998,8 +3035,12 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
+      <c r="A3" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -3008,8 +3049,12 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>107</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -5108,14 +5153,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.14" customWidth="1"/>
-    <col min="2" max="2" width="23.71" customWidth="1"/>
-    <col min="3" max="3" width="45.14" customWidth="1"/>
-    <col min="4" max="4" width="14.57" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="25.14" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="13.14"/>
+    <col min="2" max="2" customWidth="true" width="23.71"/>
+    <col min="3" max="3" customWidth="true" width="45.14"/>
+    <col min="4" max="4" customWidth="true" width="14.57"/>
+    <col min="5" max="5" customWidth="true" width="60.0"/>
+    <col min="6" max="6" customWidth="true" width="25.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7173,14 +7219,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="37.29" customWidth="1"/>
-    <col min="2" max="2" width="29.57" customWidth="1"/>
-    <col min="3" max="3" width="24.57" customWidth="1"/>
-    <col min="4" max="4" width="27.57" customWidth="1"/>
-    <col min="5" max="5" width="25.29" customWidth="1"/>
-    <col min="6" max="6" width="33.57" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="37.29"/>
+    <col min="2" max="2" customWidth="true" width="29.57"/>
+    <col min="3" max="3" customWidth="true" width="24.57"/>
+    <col min="4" max="4" customWidth="true" width="27.57"/>
+    <col min="5" max="5" customWidth="true" width="25.29"/>
+    <col min="6" max="6" customWidth="true" width="33.57"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9234,11 +9281,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.29" customWidth="1"/>
-    <col min="2" max="2" width="14.14" customWidth="1"/>
-    <col min="3" max="3" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.29"/>
+    <col min="2" max="2" customWidth="true" width="14.14"/>
+    <col min="3" max="3" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9296,13 +9344,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.43" customWidth="1"/>
-    <col min="2" max="2" width="31.43" customWidth="1"/>
-    <col min="3" max="3" width="28.71" customWidth="1"/>
-    <col min="4" max="4" width="30.57" customWidth="1"/>
-    <col min="5" max="5" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="29.43"/>
+    <col min="2" max="2" customWidth="true" width="31.43"/>
+    <col min="3" max="3" customWidth="true" width="28.71"/>
+    <col min="4" max="4" customWidth="true" width="30.57"/>
+    <col min="5" max="5" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9415,12 +9464,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.29" customWidth="1"/>
-    <col min="2" max="2" width="20.14" customWidth="1"/>
-    <col min="3" max="4" width="13.57" customWidth="1"/>
-    <col min="5" max="5" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.29"/>
+    <col min="2" max="2" customWidth="true" width="20.14"/>
+    <col min="3" max="4" customWidth="true" width="13.57"/>
+    <col min="5" max="5" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9519,11 +9569,12 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.57" customWidth="1"/>
-    <col min="2" max="2" width="39.86" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.57"/>
+    <col min="2" max="2" customWidth="true" width="39.86"/>
+    <col min="3" max="3" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9702,11 +9753,12 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="56.0"/>
+    <col min="2" max="2" customWidth="true" width="57.0"/>
+    <col min="3" max="3" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>TCID</t>
   </si>
@@ -340,28 +340,12 @@
   </si>
   <si>
     <t>Test Degree</t>
-  </si>
-  <si>
-    <t>Legal name</t>
-  </si>
-  <si>
-    <t>Test FN Automation MN Test LN</t>
-  </si>
-  <si>
-    <t>Preferred first name</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>January 23, 1962</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -433,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -456,15 +440,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -673,11 +648,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="24.57"/>
-    <col min="2" max="6" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="24.57" customWidth="1"/>
+    <col min="2" max="6" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2391,15 +2365,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="18.57"/>
-    <col min="7" max="7" customWidth="true" width="30.14"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18.57" customWidth="1"/>
+    <col min="7" max="7" width="30.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2491,14 +2464,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="14.43"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2572,14 +2544,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.14"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="41.43"/>
-    <col min="4" max="4" customWidth="true" width="34.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="27.14" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="41.43" customWidth="1"/>
+    <col min="4" max="4" width="34.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2644,10 +2615,9 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2831,10 +2801,9 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="4" customWidth="true" width="14.43"/>
+    <col min="1" max="4" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2928,14 +2897,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="31.0"/>
-    <col min="2" max="2" customWidth="true" width="27.43"/>
-    <col min="3" max="3" customWidth="true" width="51.0"/>
-    <col min="4" max="4" customWidth="true" width="22.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="27.43" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
+    <col min="4" max="4" width="22.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2997,17 +2965,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="36.86"/>
-    <col min="2" max="2" customWidth="true" width="41.14"/>
-    <col min="3" max="3" customWidth="true" width="20.43"/>
-    <col min="4" max="4" customWidth="true" width="20.14"/>
-    <col min="5" max="5" customWidth="true" width="31.43"/>
-    <col min="6" max="6" customWidth="true" width="24.43"/>
-    <col min="7" max="7" customWidth="true" width="26.71"/>
-    <col min="12" max="12" customWidth="true" width="40.71"/>
+    <col min="1" max="1" width="36.86" customWidth="1"/>
+    <col min="2" max="2" width="41.14" customWidth="1"/>
+    <col min="3" max="3" width="20.43" customWidth="1"/>
+    <col min="4" max="4" width="20.14" customWidth="1"/>
+    <col min="5" max="5" width="31.43" customWidth="1"/>
+    <col min="6" max="6" width="24.43" customWidth="1"/>
+    <col min="7" max="7" width="26.71" customWidth="1"/>
+    <col min="12" max="12" width="40.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -3021,12 +2988,8 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>104</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -3035,12 +2998,8 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -3049,12 +3008,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>107</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -5153,15 +5108,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="13.14"/>
-    <col min="2" max="2" customWidth="true" width="23.71"/>
-    <col min="3" max="3" customWidth="true" width="45.14"/>
-    <col min="4" max="4" customWidth="true" width="14.57"/>
-    <col min="5" max="5" customWidth="true" width="60.0"/>
-    <col min="6" max="6" customWidth="true" width="25.14"/>
+    <col min="1" max="1" width="13.14" customWidth="1"/>
+    <col min="2" max="2" width="23.71" customWidth="1"/>
+    <col min="3" max="3" width="45.14" customWidth="1"/>
+    <col min="4" max="4" width="14.57" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="25.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7219,15 +7173,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.29"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="24.57"/>
-    <col min="4" max="4" customWidth="true" width="27.57"/>
-    <col min="5" max="5" customWidth="true" width="25.29"/>
-    <col min="6" max="6" customWidth="true" width="33.57"/>
+    <col min="1" max="1" width="37.29" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="24.57" customWidth="1"/>
+    <col min="4" max="4" width="27.57" customWidth="1"/>
+    <col min="5" max="5" width="25.29" customWidth="1"/>
+    <col min="6" max="6" width="33.57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9281,12 +9234,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="14.14"/>
-    <col min="3" max="3" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="14.14" customWidth="1"/>
+    <col min="3" max="3" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9344,14 +9296,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="29.43"/>
-    <col min="2" max="2" customWidth="true" width="31.43"/>
-    <col min="3" max="3" customWidth="true" width="28.71"/>
-    <col min="4" max="4" customWidth="true" width="30.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="29.43" customWidth="1"/>
+    <col min="2" max="2" width="31.43" customWidth="1"/>
+    <col min="3" max="3" width="28.71" customWidth="1"/>
+    <col min="4" max="4" width="30.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9464,13 +9415,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="20.14"/>
-    <col min="3" max="4" customWidth="true" width="13.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="20.14" customWidth="1"/>
+    <col min="3" max="4" width="13.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9569,12 +9519,11 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.57"/>
-    <col min="2" max="2" customWidth="true" width="39.86"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="27.57" customWidth="1"/>
+    <col min="2" max="2" width="39.86" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9753,12 +9702,11 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="56.0"/>
-    <col min="2" max="2" customWidth="true" width="57.0"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
   <si>
     <t>TCID</t>
   </si>
@@ -340,12 +340,28 @@
   </si>
   <si>
     <t>Test Degree</t>
+  </si>
+  <si>
+    <t>Legal name</t>
+  </si>
+  <si>
+    <t>Test FN Automation MN Test LN</t>
+  </si>
+  <si>
+    <t>Preferred first name</t>
+  </si>
+  <si>
+    <t>Date of birth</t>
+  </si>
+  <si>
+    <t>November 23, 1933</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -417,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -440,6 +456,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,10 +673,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="24.57" customWidth="1"/>
-    <col min="2" max="6" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="24.57"/>
+    <col min="2" max="6" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2365,14 +2391,15 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="22.29" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="18.57" customWidth="1"/>
-    <col min="7" max="7" width="30.14" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="38.29"/>
+    <col min="3" max="3" customWidth="true" width="34.0"/>
+    <col min="4" max="4" customWidth="true" width="22.29"/>
+    <col min="5" max="5" customWidth="true" width="30.0"/>
+    <col min="6" max="6" customWidth="true" width="18.57"/>
+    <col min="7" max="7" customWidth="true" width="30.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2464,13 +2491,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="22.29" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="14.43" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="38.29"/>
+    <col min="3" max="3" customWidth="true" width="34.0"/>
+    <col min="4" max="4" customWidth="true" width="22.29"/>
+    <col min="5" max="5" customWidth="true" width="30.0"/>
+    <col min="6" max="6" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2544,13 +2572,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.14" customWidth="1"/>
-    <col min="2" max="2" width="29.57" customWidth="1"/>
-    <col min="3" max="3" width="41.43" customWidth="1"/>
-    <col min="4" max="4" width="34.43" customWidth="1"/>
-    <col min="5" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.14"/>
+    <col min="2" max="2" customWidth="true" width="29.57"/>
+    <col min="3" max="3" customWidth="true" width="41.43"/>
+    <col min="4" max="4" customWidth="true" width="34.43"/>
+    <col min="5" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2615,9 +2644,10 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2801,9 +2831,10 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="14.43" customWidth="1"/>
+    <col min="1" max="4" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2897,13 +2928,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="27.43" customWidth="1"/>
-    <col min="3" max="3" width="51" customWidth="1"/>
-    <col min="4" max="4" width="22.43" customWidth="1"/>
-    <col min="5" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="31.0"/>
+    <col min="2" max="2" customWidth="true" width="27.43"/>
+    <col min="3" max="3" customWidth="true" width="51.0"/>
+    <col min="4" max="4" customWidth="true" width="22.43"/>
+    <col min="5" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2965,16 +2997,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="36.86" customWidth="1"/>
-    <col min="2" max="2" width="41.14" customWidth="1"/>
-    <col min="3" max="3" width="20.43" customWidth="1"/>
-    <col min="4" max="4" width="20.14" customWidth="1"/>
-    <col min="5" max="5" width="31.43" customWidth="1"/>
-    <col min="6" max="6" width="24.43" customWidth="1"/>
-    <col min="7" max="7" width="26.71" customWidth="1"/>
-    <col min="12" max="12" width="40.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="36.86"/>
+    <col min="2" max="2" customWidth="true" width="41.14"/>
+    <col min="3" max="3" customWidth="true" width="20.43"/>
+    <col min="4" max="4" customWidth="true" width="20.14"/>
+    <col min="5" max="5" customWidth="true" width="31.43"/>
+    <col min="6" max="6" customWidth="true" width="24.43"/>
+    <col min="7" max="7" customWidth="true" width="26.71"/>
+    <col min="12" max="12" customWidth="true" width="40.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -2988,8 +3021,12 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="3"/>
+      <c r="A2" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -2998,8 +3035,12 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" s="1"/>
-      <c r="B3" s="3"/>
+      <c r="A3" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>29</v>
+      </c>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -3008,8 +3049,12 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3"/>
+      <c r="A4" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>107</v>
+      </c>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>
@@ -5108,14 +5153,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.14" customWidth="1"/>
-    <col min="2" max="2" width="23.71" customWidth="1"/>
-    <col min="3" max="3" width="45.14" customWidth="1"/>
-    <col min="4" max="4" width="14.57" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="25.14" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="13.14"/>
+    <col min="2" max="2" customWidth="true" width="23.71"/>
+    <col min="3" max="3" customWidth="true" width="45.14"/>
+    <col min="4" max="4" customWidth="true" width="14.57"/>
+    <col min="5" max="5" customWidth="true" width="60.0"/>
+    <col min="6" max="6" customWidth="true" width="25.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7173,14 +7219,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="37.29" customWidth="1"/>
-    <col min="2" max="2" width="29.57" customWidth="1"/>
-    <col min="3" max="3" width="24.57" customWidth="1"/>
-    <col min="4" max="4" width="27.57" customWidth="1"/>
-    <col min="5" max="5" width="25.29" customWidth="1"/>
-    <col min="6" max="6" width="33.57" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="37.29"/>
+    <col min="2" max="2" customWidth="true" width="29.57"/>
+    <col min="3" max="3" customWidth="true" width="24.57"/>
+    <col min="4" max="4" customWidth="true" width="27.57"/>
+    <col min="5" max="5" customWidth="true" width="25.29"/>
+    <col min="6" max="6" customWidth="true" width="33.57"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9234,11 +9281,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.29" customWidth="1"/>
-    <col min="2" max="2" width="14.14" customWidth="1"/>
-    <col min="3" max="3" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.29"/>
+    <col min="2" max="2" customWidth="true" width="14.14"/>
+    <col min="3" max="3" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9296,13 +9344,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.43" customWidth="1"/>
-    <col min="2" max="2" width="31.43" customWidth="1"/>
-    <col min="3" max="3" width="28.71" customWidth="1"/>
-    <col min="4" max="4" width="30.57" customWidth="1"/>
-    <col min="5" max="5" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="29.43"/>
+    <col min="2" max="2" customWidth="true" width="31.43"/>
+    <col min="3" max="3" customWidth="true" width="28.71"/>
+    <col min="4" max="4" customWidth="true" width="30.57"/>
+    <col min="5" max="5" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9415,12 +9464,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.29" customWidth="1"/>
-    <col min="2" max="2" width="20.14" customWidth="1"/>
-    <col min="3" max="4" width="13.57" customWidth="1"/>
-    <col min="5" max="5" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.29"/>
+    <col min="2" max="2" customWidth="true" width="20.14"/>
+    <col min="3" max="4" customWidth="true" width="13.57"/>
+    <col min="5" max="5" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9519,11 +9569,12 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.57" customWidth="1"/>
-    <col min="2" max="2" width="39.86" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.57"/>
+    <col min="2" max="2" customWidth="true" width="39.86"/>
+    <col min="3" max="3" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9702,11 +9753,12 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="56.0"/>
+    <col min="2" max="2" customWidth="true" width="57.0"/>
+    <col min="3" max="3" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>TCID</t>
   </si>
@@ -342,19 +342,10 @@
     <t>Test Degree</t>
   </si>
   <si>
-    <t>Legal name</t>
-  </si>
-  <si>
-    <t>Test FN Automation MN Test LN</t>
-  </si>
-  <si>
-    <t>Preferred first name</t>
-  </si>
-  <si>
-    <t>Date of birth</t>
-  </si>
-  <si>
-    <t>November 23, 1933</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>2063622@test.asu.edu</t>
   </si>
 </sst>
 </file>
@@ -433,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -456,12 +447,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
     </xf>
@@ -3011,7 +2996,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="B1" s="3"/>
+      <c r="A1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -3021,12 +3011,8 @@
       <c r="L1" s="3"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>104</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3"/>
@@ -3035,12 +3021,8 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="14.25" customHeight="1">
-      <c r="A3" t="s" s="0">
-        <v>105</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>29</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="3"/>
@@ -3049,12 +3031,8 @@
       <c r="L3" s="3"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
-      <c r="A4" t="s" s="0">
-        <v>106</v>
-      </c>
-      <c r="B4" s="16" t="s">
-        <v>107</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="3"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="3"/>

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>TCID</t>
   </si>
@@ -340,19 +340,12 @@
   </si>
   <si>
     <t>Test Degree</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>2063622@test.asu.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -424,7 +417,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -447,9 +440,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment wrapText="true"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,11 +648,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="24.57"/>
-    <col min="2" max="6" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="24.57" customWidth="1"/>
+    <col min="2" max="6" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2376,15 +2365,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="18.57"/>
-    <col min="7" max="7" customWidth="true" width="30.14"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18.57" customWidth="1"/>
+    <col min="7" max="7" width="30.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2476,14 +2464,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" customWidth="true" width="38.29"/>
-    <col min="3" max="3" customWidth="true" width="34.0"/>
-    <col min="4" max="4" customWidth="true" width="22.29"/>
-    <col min="5" max="5" customWidth="true" width="30.0"/>
-    <col min="6" max="6" customWidth="true" width="14.43"/>
+    <col min="1" max="2" width="38.29" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="22.29" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2557,14 +2544,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.14"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="41.43"/>
-    <col min="4" max="4" customWidth="true" width="34.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="27.14" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="41.43" customWidth="1"/>
+    <col min="4" max="4" width="34.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2629,10 +2615,9 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2816,10 +2801,9 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="4" customWidth="true" width="14.43"/>
+    <col min="1" max="4" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2913,14 +2897,13 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="31.0"/>
-    <col min="2" max="2" customWidth="true" width="27.43"/>
-    <col min="3" max="3" customWidth="true" width="51.0"/>
-    <col min="4" max="4" customWidth="true" width="22.43"/>
-    <col min="5" max="5" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="27.43" customWidth="1"/>
+    <col min="3" max="3" width="51" customWidth="1"/>
+    <col min="4" max="4" width="22.43" customWidth="1"/>
+    <col min="5" max="5" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2982,26 +2965,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="36.86"/>
-    <col min="2" max="2" customWidth="true" width="41.14"/>
-    <col min="3" max="3" customWidth="true" width="20.43"/>
-    <col min="4" max="4" customWidth="true" width="20.14"/>
-    <col min="5" max="5" customWidth="true" width="31.43"/>
-    <col min="6" max="6" customWidth="true" width="24.43"/>
-    <col min="7" max="7" customWidth="true" width="26.71"/>
-    <col min="12" max="12" customWidth="true" width="40.71"/>
+    <col min="1" max="1" width="36.86" customWidth="1"/>
+    <col min="2" max="2" width="41.14" customWidth="1"/>
+    <col min="3" max="3" width="20.43" customWidth="1"/>
+    <col min="4" max="4" width="20.14" customWidth="1"/>
+    <col min="5" max="5" width="31.43" customWidth="1"/>
+    <col min="6" max="6" width="24.43" customWidth="1"/>
+    <col min="7" max="7" width="26.71" customWidth="1"/>
+    <col min="12" max="12" width="40.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" t="s" s="0">
-        <v>103</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>104</v>
-      </c>
+      <c r="B1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -5131,15 +5108,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="13.14"/>
-    <col min="2" max="2" customWidth="true" width="23.71"/>
-    <col min="3" max="3" customWidth="true" width="45.14"/>
-    <col min="4" max="4" customWidth="true" width="14.57"/>
-    <col min="5" max="5" customWidth="true" width="60.0"/>
-    <col min="6" max="6" customWidth="true" width="25.14"/>
+    <col min="1" max="1" width="13.14" customWidth="1"/>
+    <col min="2" max="2" width="23.71" customWidth="1"/>
+    <col min="3" max="3" width="45.14" customWidth="1"/>
+    <col min="4" max="4" width="14.57" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="6" max="6" width="25.14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7197,15 +7173,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="37.29"/>
-    <col min="2" max="2" customWidth="true" width="29.57"/>
-    <col min="3" max="3" customWidth="true" width="24.57"/>
-    <col min="4" max="4" customWidth="true" width="27.57"/>
-    <col min="5" max="5" customWidth="true" width="25.29"/>
-    <col min="6" max="6" customWidth="true" width="33.57"/>
+    <col min="1" max="1" width="37.29" customWidth="1"/>
+    <col min="2" max="2" width="29.57" customWidth="1"/>
+    <col min="3" max="3" width="24.57" customWidth="1"/>
+    <col min="4" max="4" width="27.57" customWidth="1"/>
+    <col min="5" max="5" width="25.29" customWidth="1"/>
+    <col min="6" max="6" width="33.57" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9259,12 +9234,11 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="14.14"/>
-    <col min="3" max="3" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="14.14" customWidth="1"/>
+    <col min="3" max="3" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9322,14 +9296,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="29.43"/>
-    <col min="2" max="2" customWidth="true" width="31.43"/>
-    <col min="3" max="3" customWidth="true" width="28.71"/>
-    <col min="4" max="4" customWidth="true" width="30.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="29.43" customWidth="1"/>
+    <col min="2" max="2" width="31.43" customWidth="1"/>
+    <col min="3" max="3" width="28.71" customWidth="1"/>
+    <col min="4" max="4" width="30.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9442,13 +9415,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.29"/>
-    <col min="2" max="2" customWidth="true" width="20.14"/>
-    <col min="3" max="4" customWidth="true" width="13.57"/>
-    <col min="5" max="5" customWidth="true" width="8.71"/>
+    <col min="1" max="1" width="27.29" customWidth="1"/>
+    <col min="2" max="2" width="20.14" customWidth="1"/>
+    <col min="3" max="4" width="13.57" customWidth="1"/>
+    <col min="5" max="5" width="8.71" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9547,12 +9519,11 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="27.57"/>
-    <col min="2" max="2" customWidth="true" width="39.86"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="27.57" customWidth="1"/>
+    <col min="2" max="2" width="39.86" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9731,12 +9702,11 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="56.0"/>
-    <col min="2" max="2" customWidth="true" width="57.0"/>
-    <col min="3" max="3" customWidth="true" width="14.43"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="57" customWidth="1"/>
+    <col min="3" max="3" width="14.43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">

--- a/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
+++ b/UAA/src/src/test/resources/com/ugapp/excel/testdata.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>TCID</t>
   </si>
@@ -340,12 +340,19 @@
   </si>
   <si>
     <t>Test Degree</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>7104246@test.asu.edu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="9">
     <font>
       <sz val="11"/>
@@ -417,7 +424,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -440,6 +447,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -648,10 +658,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="24.57" customWidth="1"/>
-    <col min="2" max="6" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="24.57"/>
+    <col min="2" max="6" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2365,14 +2376,15 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="22.29" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="18.57" customWidth="1"/>
-    <col min="7" max="7" width="30.14" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="38.29"/>
+    <col min="3" max="3" customWidth="true" width="34.0"/>
+    <col min="4" max="4" customWidth="true" width="22.29"/>
+    <col min="5" max="5" customWidth="true" width="30.0"/>
+    <col min="6" max="6" customWidth="true" width="18.57"/>
+    <col min="7" max="7" customWidth="true" width="30.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2464,13 +2476,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="2" width="38.29" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="22.29" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="14.43" customWidth="1"/>
+    <col min="1" max="2" customWidth="true" width="38.29"/>
+    <col min="3" max="3" customWidth="true" width="34.0"/>
+    <col min="4" max="4" customWidth="true" width="22.29"/>
+    <col min="5" max="5" customWidth="true" width="30.0"/>
+    <col min="6" max="6" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2544,13 +2557,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.14" customWidth="1"/>
-    <col min="2" max="2" width="29.57" customWidth="1"/>
-    <col min="3" max="3" width="41.43" customWidth="1"/>
-    <col min="4" max="4" width="34.43" customWidth="1"/>
-    <col min="5" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.14"/>
+    <col min="2" max="2" customWidth="true" width="29.57"/>
+    <col min="3" max="3" customWidth="true" width="41.43"/>
+    <col min="4" max="4" customWidth="true" width="34.43"/>
+    <col min="5" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2615,9 +2629,10 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2801,9 +2816,10 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="4" width="14.43" customWidth="1"/>
+    <col min="1" max="4" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2897,13 +2913,14 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="31" customWidth="1"/>
-    <col min="2" max="2" width="27.43" customWidth="1"/>
-    <col min="3" max="3" width="51" customWidth="1"/>
-    <col min="4" max="4" width="22.43" customWidth="1"/>
-    <col min="5" max="5" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="31.0"/>
+    <col min="2" max="2" customWidth="true" width="27.43"/>
+    <col min="3" max="3" customWidth="true" width="51.0"/>
+    <col min="4" max="4" customWidth="true" width="22.43"/>
+    <col min="5" max="5" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -2965,20 +2982,26 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="36.86" customWidth="1"/>
-    <col min="2" max="2" width="41.14" customWidth="1"/>
-    <col min="3" max="3" width="20.43" customWidth="1"/>
-    <col min="4" max="4" width="20.14" customWidth="1"/>
-    <col min="5" max="5" width="31.43" customWidth="1"/>
-    <col min="6" max="6" width="24.43" customWidth="1"/>
-    <col min="7" max="7" width="26.71" customWidth="1"/>
-    <col min="12" max="12" width="40.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="36.86"/>
+    <col min="2" max="2" customWidth="true" width="41.14"/>
+    <col min="3" max="3" customWidth="true" width="20.43"/>
+    <col min="4" max="4" customWidth="true" width="20.14"/>
+    <col min="5" max="5" customWidth="true" width="31.43"/>
+    <col min="6" max="6" customWidth="true" width="24.43"/>
+    <col min="7" max="7" customWidth="true" width="26.71"/>
+    <col min="12" max="12" customWidth="true" width="40.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="B1" s="3"/>
+      <c r="A1" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>104</v>
+      </c>
       <c r="D1" s="3"/>
       <c r="E1" s="1"/>
       <c r="F1" s="3"/>
@@ -5108,14 +5131,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.14" customWidth="1"/>
-    <col min="2" max="2" width="23.71" customWidth="1"/>
-    <col min="3" max="3" width="45.14" customWidth="1"/>
-    <col min="4" max="4" width="14.57" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="25.14" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="13.14"/>
+    <col min="2" max="2" customWidth="true" width="23.71"/>
+    <col min="3" max="3" customWidth="true" width="45.14"/>
+    <col min="4" max="4" customWidth="true" width="14.57"/>
+    <col min="5" max="5" customWidth="true" width="60.0"/>
+    <col min="6" max="6" customWidth="true" width="25.14"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -7173,14 +7197,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:L1000"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="37.29" customWidth="1"/>
-    <col min="2" max="2" width="29.57" customWidth="1"/>
-    <col min="3" max="3" width="24.57" customWidth="1"/>
-    <col min="4" max="4" width="27.57" customWidth="1"/>
-    <col min="5" max="5" width="25.29" customWidth="1"/>
-    <col min="6" max="6" width="33.57" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="37.29"/>
+    <col min="2" max="2" customWidth="true" width="29.57"/>
+    <col min="3" max="3" customWidth="true" width="24.57"/>
+    <col min="4" max="4" customWidth="true" width="27.57"/>
+    <col min="5" max="5" customWidth="true" width="25.29"/>
+    <col min="6" max="6" customWidth="true" width="33.57"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9234,11 +9259,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.29" customWidth="1"/>
-    <col min="2" max="2" width="14.14" customWidth="1"/>
-    <col min="3" max="3" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.29"/>
+    <col min="2" max="2" customWidth="true" width="14.14"/>
+    <col min="3" max="3" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9296,13 +9322,14 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="29.43" customWidth="1"/>
-    <col min="2" max="2" width="31.43" customWidth="1"/>
-    <col min="3" max="3" width="28.71" customWidth="1"/>
-    <col min="4" max="4" width="30.57" customWidth="1"/>
-    <col min="5" max="5" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="29.43"/>
+    <col min="2" max="2" customWidth="true" width="31.43"/>
+    <col min="3" max="3" customWidth="true" width="28.71"/>
+    <col min="4" max="4" customWidth="true" width="30.57"/>
+    <col min="5" max="5" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
@@ -9415,12 +9442,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.29" customWidth="1"/>
-    <col min="2" max="2" width="20.14" customWidth="1"/>
-    <col min="3" max="4" width="13.57" customWidth="1"/>
-    <col min="5" max="5" width="8.71" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.29"/>
+    <col min="2" max="2" customWidth="true" width="20.14"/>
+    <col min="3" max="4" customWidth="true" width="13.57"/>
+    <col min="5" max="5" customWidth="true" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9519,11 +9547,12 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.57" customWidth="1"/>
-    <col min="2" max="2" width="39.86" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="27.57"/>
+    <col min="2" max="2" customWidth="true" width="39.86"/>
+    <col min="3" max="3" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -9702,11 +9731,12 @@
   <sheetPr>
     <outlinePr summaryRight="0" summaryBelow="0"/>
   </sheetPr>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="57" customWidth="1"/>
-    <col min="3" max="3" width="14.43" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="56.0"/>
+    <col min="2" max="2" customWidth="true" width="57.0"/>
+    <col min="3" max="3" customWidth="true" width="14.43"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
